--- a/Case_studies/Case_study_2-Bo_et_al_2011.xlsx
+++ b/Case_studies/Case_study_2-Bo_et_al_2011.xlsx
@@ -1,26 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://univpm-my.sharepoint.com/personal/s1116344_pm_univpm_it/Documents/PhD/ASMR/Case_studies/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\claud\Documents\COMUNE\STUDIO_LAVORO\Data_analysis\Projects\ASMR\Case_studies\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="8_{C7C4B3F3-C924-45AD-BB41-A3CF1BA542F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D841FB75-210C-470F-8E73-6582FFB11C38}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B8160C-3CB5-4C0F-B92D-507E4ECCCB10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{C772E4A6-6938-4714-B988-E5854FC383F1}"/>
   </bookViews>
   <sheets>
-    <sheet name="event" sheetId="1" r:id="rId1"/>
-    <sheet name="project" sheetId="7" r:id="rId2"/>
+    <sheet name="Full" sheetId="8" r:id="rId1"/>
+    <sheet name="event" sheetId="1" r:id="rId2"/>
     <sheet name="occurrence" sheetId="2" r:id="rId3"/>
     <sheet name="humboldt" sheetId="3" r:id="rId4"/>
     <sheet name="extendedmeasurementorfact" sheetId="5" r:id="rId5"/>
-    <sheet name="asmr" sheetId="4" r:id="rId6"/>
-    <sheet name="Sheet1" sheetId="6" r:id="rId7"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Full!$A$1:$Q$165</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -45,6 +47,51 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={BBEAE2E5-2B03-43BD-B0A8-9BC6843E9ADC}</author>
+    <author>tc={88C3F7A2-0849-4EAC-9403-E876BF64BDD2}</author>
+    <author>tc={3B269ACA-71E5-4733-9E6C-3A5752A3F20B}</author>
+    <author>tc={B72C3B60-DE4A-428A-842F-0321C07BC243}</author>
+  </authors>
+  <commentList>
+    <comment ref="P62" authorId="0" shapeId="0" xr:uid="{BBEAE2E5-2B03-43BD-B0A8-9BC6843E9ADC}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Check humboldt use case</t>
+      </text>
+    </comment>
+    <comment ref="P86" authorId="1" shapeId="0" xr:uid="{88C3F7A2-0849-4EAC-9403-E876BF64BDD2}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Same as model?</t>
+      </text>
+    </comment>
+    <comment ref="P103" authorId="2" shapeId="0" xr:uid="{3B269ACA-71E5-4733-9E6C-3A5752A3F20B}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Definition!?</t>
+      </text>
+    </comment>
+    <comment ref="P122" authorId="3" shapeId="0" xr:uid="{B72C3B60-DE4A-428A-842F-0321C07BC243}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    HUMBOLDT USE CASE</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={F778C68F-B3AA-49A7-8F4C-181180D98A3B}</author>
@@ -81,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1648" uniqueCount="727">
   <si>
     <t>id</t>
   </si>
@@ -308,34 +355,7 @@
     <t>measurementUnitID</t>
   </si>
   <si>
-    <t>BROKE_WEST</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>2006-01-02/2006-03-17</t>
-  </si>
-  <si>
-    <t>Krills caught are recorded in another dataset: http://dx.doi.org/doi:10.4225/15/57BBAF89ECD5D</t>
-  </si>
-  <si>
-    <t>Southern Ocean</t>
-  </si>
-  <si>
-    <t>AQ</t>
-  </si>
-  <si>
-    <t>CCAMLR Subdivision 58.4.2 of the Southern Ocean; includes the Cosmonaut Sea to the west and Prydz Bay area to the east</t>
-  </si>
-  <si>
     <t>WGS84</t>
-  </si>
-  <si>
-    <t>POLYGON((30 -69, 30 -32,147 -32, 147 -69))</t>
-  </si>
-  <si>
-    <t>EPSG:4326</t>
   </si>
   <si>
     <t>VERCELLI_SEAMOUNT_PINNACLE</t>
@@ -863,12 +883,1887 @@
   <si>
     <t>dwc:eventID</t>
   </si>
+  <si>
+    <t>data_type</t>
+  </si>
+  <si>
+    <t>section</t>
+  </si>
+  <si>
+    <t>term</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>comment</t>
+  </si>
+  <si>
+    <t>requirement_level</t>
+  </si>
+  <si>
+    <t>requirement_level_condition</t>
+  </si>
+  <si>
+    <t>term_type</t>
+  </si>
+  <si>
+    <t>unit</t>
+  </si>
+  <si>
+    <t>fixed_format</t>
+  </si>
+  <si>
+    <t>controlled_vocabulary_options</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>source</t>
+  </si>
+  <si>
+    <t>URI</t>
+  </si>
+  <si>
+    <t>modifications_made</t>
+  </si>
+  <si>
+    <t>Bo_et_al_2011</t>
+  </si>
+  <si>
+    <t>projectMetadata</t>
+  </si>
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>dwc:recordedBy</t>
+  </si>
+  <si>
+    <t>A list (concatenated and separated) of names of people responsible for the submitted dataset (e.g. eDNA) or dwc:Occurrence</t>
+  </si>
+  <si>
+    <t>Mandatory</t>
+  </si>
+  <si>
+    <t>free text</t>
+  </si>
+  <si>
+    <t>José E. Crespo</t>
+  </si>
+  <si>
+    <t>DwC</t>
+  </si>
+  <si>
+    <t>https://dwc.tdwg.org/list/#dwc_recordedBy</t>
+  </si>
+  <si>
+    <t>Claudia Campanini</t>
+  </si>
+  <si>
+    <t>dwc:recordedByID</t>
+  </si>
+  <si>
+    <t>A list (concatenated and separated) of the globally unique identifier for the people responsible for the submitted dataset or dwc:Occurrence</t>
+  </si>
+  <si>
+    <t>Recommended</t>
+  </si>
+  <si>
+    <t>https://orcid.org/0000-0002-1825-0097  |  https://orcid.org/0000-0002-1825-0098</t>
+  </si>
+  <si>
+    <t>https://dwc.tdwg.org/list/#dwc_recordedByID</t>
+  </si>
+  <si>
+    <t>https://orcid.org/0000-0002-4242-5862</t>
+  </si>
+  <si>
+    <t>edna:project_contact</t>
+  </si>
+  <si>
+    <t>A contact person and their contact (i.e., email address) for data enquiry</t>
+  </si>
+  <si>
+    <t>xxxx@yyyy.com</t>
+  </si>
+  <si>
+    <t>Fair eDNA</t>
+  </si>
+  <si>
+    <t>m.bo@univpm.it</t>
+  </si>
+  <si>
+    <t>dwc:institutionID</t>
+  </si>
+  <si>
+    <t>An identifier for the institution having custody of the object(s) or information referred to in the record. This identifier should point to a persistent, resolvable identifier, such as a Research Organization Registry (ROR) ID or ISNI (International Standard Name Identifier).</t>
+  </si>
+  <si>
+    <t>https://ror.org/042r9xb17</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/dwc/terms/institutionID</t>
+  </si>
+  <si>
+    <t>dwc:projectTitle</t>
+  </si>
+  <si>
+    <t>Name of the project within which the sequencing was organized</t>
+  </si>
+  <si>
+    <t>Forest soil metagenome</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/dwc/terms/projectTitle</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PRIN (Progetti di Rilevante Interesse Nazionale) project Tyrrhenian Seamounts ecosystems: an Integrated Study (TySEc)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> financed by the Italian Ministry of Research and by the Global Census of Marine Life on Seamounts (CenSeam, New Zealand)</t>
+    </r>
+  </si>
+  <si>
+    <t>dwc:projectID</t>
+  </si>
+  <si>
+    <t>A brief, concise project identifier with no spaces or special characters, ensuring machine readability. This ID will be used in data file names as 'project_id'.</t>
+  </si>
+  <si>
+    <t>noaa-aoml-gomecc4</t>
+  </si>
+  <si>
+    <t>https://w3id.org/nmdc/project_id</t>
+  </si>
+  <si>
+    <t>edna:parent_project_id</t>
+  </si>
+  <si>
+    <t>An identifier or name of the overarching (parent) project that encompasses and organizes multiple related sub-projects, each identified by a unique project_id</t>
+  </si>
+  <si>
+    <t>Optional</t>
+  </si>
+  <si>
+    <t>noaa-aoml-gomecc</t>
+  </si>
+  <si>
+    <t>Data management</t>
+  </si>
+  <si>
+    <t>dcterms:license</t>
+  </si>
+  <si>
+    <t>A legal document giving official permission to do something with the resource.</t>
+  </si>
+  <si>
+    <t>http://creativecommons.org/licenses/by/4.0/legalcode</t>
+  </si>
+  <si>
+    <t>Dublin Core</t>
+  </si>
+  <si>
+    <t>http://purl.org/dc/terms/license</t>
+  </si>
+  <si>
+    <t>Creative Commons Attribution License</t>
+  </si>
+  <si>
+    <t>dcterms:rightsHolder</t>
+  </si>
+  <si>
+    <t>A person or organization owning or managing rights over the resource.</t>
+  </si>
+  <si>
+    <t>The Regents of the University of California</t>
+  </si>
+  <si>
+    <t>http://purl.org/dc/terms/rightsHolder</t>
+  </si>
+  <si>
+    <t>Marzia Bo | Marco Bertolino | Mireno Borghini | Michela Castellano| Anabella Covazzi Harriague |Cristina Gioia Di Camillo |GianPietro Gasparini |Cristina Misic | Paolo Povero | Antonio Pusceddu | Katrin Schroeder | Giorgio Bavestrello</t>
+  </si>
+  <si>
+    <t>dcterms::accessRights</t>
+  </si>
+  <si>
+    <t>Information about who can access the resource or an indication of its security status.</t>
+  </si>
+  <si>
+    <t>not-for-profit use only </t>
+  </si>
+  <si>
+    <t>http://purl.org/dc/terms/accessRights</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>dwc:informationWithheld</t>
+  </si>
+  <si>
+    <t>Additional information that exists, but that has not been shared in the given record.</t>
+  </si>
+  <si>
+    <t>location information not given for endangered species</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/dwc/terms/informationWithheld</t>
+  </si>
+  <si>
+    <t>unrestricted use, distribution, and reproduction in any medium, provided the original author and source are credited.</t>
+  </si>
+  <si>
+    <t>dwc:dataGeneralizations</t>
+  </si>
+  <si>
+    <t>Actions taken to make the shared data (i.e. location, date) less specific or complete than in its original form. Suggests that alternative data of higher quality may be available on request. Note this is not related to genetic generalisation within bioinformatic workflows (i.e., OTU clustering).</t>
+  </si>
+  <si>
+    <t>Coordinates generalized from original GPS coordinates to the nearest half degree grid cell.</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/dwc/terms/dataGeneralizations</t>
+  </si>
+  <si>
+    <t>Habitat generlized from original description to compile the asmr:standardHabitatValue, eco:targetHabitatScope, according to the asmr:habitatClassificationScheme, i.e. Interpretation Manual of Marine Habitat Types in the Mediterranean Sea (UNEP-MAP RAC/SPA, 2021). The standardized habitat and facies theoretically only applies to circalittoral coastal environments and not seamount, but the habitat described in the article more closely resemble the coastal coralligenous cliffs</t>
+  </si>
+  <si>
+    <t>dcterms:bibliographicCitation</t>
+  </si>
+  <si>
+    <t>A bibliographic reference for the resource.</t>
+  </si>
+  <si>
+    <t>From Dublin Core, "Recommended practice is to include sufficient bibliographic detail to identify the resource as unambiguously as possible." The intended usage of this term in Darwin Core is to provide the preferred way to cite the resource itself - "how to cite this record". Note that the intended usage of dcterms:references in Darwin Core, by contrast, is to point to the definitive source representation of the resource - "where to find the as-close-to-original reference", if one is available.</t>
+  </si>
+  <si>
+    <t>DOI</t>
+  </si>
+  <si>
+    <t>DOI: 10.1111/mec.15382</t>
+  </si>
+  <si>
+    <t>http://purl.org/dc/terms/bibliographicCitation</t>
+  </si>
+  <si>
+    <t>MIxS:associated_resource</t>
+  </si>
+  <si>
+    <t>A related resource that is referenced, cited, or otherwise associated to the sequence. i.e., links to a project website, submitted raw sequence data and environmental metadata.</t>
+  </si>
+  <si>
+    <t>http://www.earthmicrobiome.org/</t>
+  </si>
+  <si>
+    <t>MIxS</t>
+  </si>
+  <si>
+    <t>https://w3id.org/mixs/0000091</t>
+  </si>
+  <si>
+    <t>code_repo</t>
+  </si>
+  <si>
+    <t>Link to public repository where analysis code is archived</t>
+  </si>
+  <si>
+    <t>https://github.com/aomlomics/gomecc</t>
+  </si>
+  <si>
+    <t>NOAA</t>
+  </si>
+  <si>
+    <t>sampleMetadata</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>dwc:decimalLongitude</t>
+  </si>
+  <si>
+    <t>The geographic longitude in decimal degrees using WGS84 datum. Positive values are east of the Greenwich Meridian, negative values are west of it. Legal values lie between -180 and 180, inclusive. The desired minimum number of decimal places is the hundred-thousandth (0.00001) to achieve meter scale resolution.</t>
+  </si>
+  <si>
+    <t>Mandatory unless specified under the term informationWithheld, or samp_category = negative control, positive control, or PCR standard</t>
+  </si>
+  <si>
+    <t>numeric</t>
+  </si>
+  <si>
+    <t>-121.17611</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/dwc/terms/decimalLongitude</t>
+  </si>
+  <si>
+    <t>dwc:decimalLatitude</t>
+  </si>
+  <si>
+    <t>The geographic latitude in decimal degrees using WGS84 datum. Positive values are north of the Equator, negative values are south of it. Legal values lie between -90 and 90, inclusive. The desired minimum number of decimal places is the hundred-thousandth (0.00001) to achieve meter scale resolution.</t>
+  </si>
+  <si>
+    <t>-41.09834</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/dwc/terms/decimalLatitude</t>
+  </si>
+  <si>
+    <t>dwc:verbatimLongitude</t>
+  </si>
+  <si>
+    <t>The original longitude in any format (i.e. deg/min/sec, UTM) before converting to decimal degrees and WGS84. verbatimCoordinateSystem and verbatimGeodeticDatum should be stored as well.</t>
+  </si>
+  <si>
+    <t>121d 10' 34" W</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/dwc/terms/verbatimLongitude</t>
+  </si>
+  <si>
+    <t>10°54.43′E</t>
+  </si>
+  <si>
+    <t>dwc:verbatimLatitude</t>
+  </si>
+  <si>
+    <t>The original latitude in any format (i.e. deg/min/sec, UTM) before converting to decimal degrees and WGS84. verbatimCoordinateSystem and verbatimGeodeticDatum should be stored as well.</t>
+  </si>
+  <si>
+    <t>41 05 54.03S</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/dwc/terms/verbatimLatitude</t>
+  </si>
+  <si>
+    <t>41°06.45′N</t>
+  </si>
+  <si>
+    <t>dwc:verbatimCoordinateSystem</t>
+  </si>
+  <si>
+    <t>The coordinate format of the verbatimLatitude and verbatimLongitude</t>
+  </si>
+  <si>
+    <t>controlled vocabulary</t>
+  </si>
+  <si>
+    <t>decimal degrees | degrees minutes seconds | UTM | other:</t>
+  </si>
+  <si>
+    <t>degrees minutes seconds</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/dwc/terms/verbatimCoordinateSystem</t>
+  </si>
+  <si>
+    <t>description | field_type</t>
+  </si>
+  <si>
+    <t>Degrees Minutes</t>
+  </si>
+  <si>
+    <t>dwc:verbatimSRS</t>
+  </si>
+  <si>
+    <t>The ellipsoid, geodetic datum, or spatial reference system (SRS) upon which coordinates given in verbatimLatitude and verbatimLongitude, or verbatimCoordinates are based.</t>
+  </si>
+  <si>
+    <t>WGS84 | NAD84 | NAD27 | GDA94 | GDA2020 | ETRS89 | JGD2000 | other:</t>
+  </si>
+  <si>
+    <t>NAD84</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/dwc/terms/verbatimSRS</t>
+  </si>
+  <si>
+    <t>Total number of individual sites surveyed during the dwc:Event.</t>
+  </si>
+  <si>
+    <t>Site refers to the location at which observations are made or samples/measurements are taken. The site can be at any level of hierarchy.</t>
+  </si>
+  <si>
+    <t>Humboldt extension</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/siteCount</t>
+  </si>
+  <si>
+    <t>Original textual description of the site(s).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Site refers to the location at which observations are made or samples/measurements are taken. The site can be at any level of hierarchy. Recommended best practice is to separate multiple values in a list with space vertical bar space ( | ).</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/verbatimSiteDescriptions</t>
+  </si>
+  <si>
+    <t>A list (concatenated and separated) of original site names.</t>
+  </si>
+  <si>
+    <t>Site refers to the location at which observations are made or samples/measurements are taken. The site can be at any level of hierarchy. Recommended best practice is to separate multiple values in a list with space vertical bar space ( | ).</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/verbatimSiteNames</t>
+  </si>
+  <si>
+    <t>The numeric value for the total area of the geospatial scope of the dwc:Event.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Geospatial scope refers to the dwc:Event location reported using the terms organized in Darwin Core under dcterms:Location. This area is always greater than or equal to the eco:totalAreaSampledValue. An eco:geospatialScopeAreaValue must have a corresponding eco:geospatialScopeAreaUnit.</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/geospatialScopeAreaValue</t>
+  </si>
+  <si>
+    <t>The units associated with eco:geospatialScopeAreaValue</t>
+  </si>
+  <si>
+    <t>Recommended best practice is to use a controlled vocabulary. For units containing exponents, use characters from the Unicode Latin-1 Supplement character set (hex 00B2 for squared and 00B3 for cubed). This term has an equivalent in the ecoiri: namespace that allows only an IRI as a value, whereas this term allows for any string literal value.</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/geospatialScopeAreaUnit</t>
+  </si>
+  <si>
+    <t>asmr:ecoregionScheme</t>
+  </si>
+  <si>
+    <t>Applied ecoregion classification scheme for asmr:ecoregionName and asmr:ecoregionCode</t>
+  </si>
+  <si>
+    <t>Terrestrial Ecoregion of the World, TEOW (Olson et al., 2001) |
+Marine Ecoregions of the World, MEOW (Spalding et al., 2007)</t>
+  </si>
+  <si>
+    <t>ASMR</t>
+  </si>
+  <si>
+    <t>Marine Ecoregions of the World, MEOW (Spalding et al., 2007)</t>
+  </si>
+  <si>
+    <t>asmr:ecoregionName</t>
+  </si>
+  <si>
+    <t>Ecoregion name according to asmr:ecoregionScheme</t>
+  </si>
+  <si>
+    <t>Western Mediterranean Sea</t>
+  </si>
+  <si>
+    <t>asmr:ecoregionCode</t>
+  </si>
+  <si>
+    <t>Ecoregion code associated to asmr:ecoregionName according to asmr:ecoregionScheme</t>
+  </si>
+  <si>
+    <t>asmr:standardGeographicFeatureClassification</t>
+  </si>
+  <si>
+    <t>If not present in the list, specify "Other:"</t>
+  </si>
+  <si>
+    <t>Marine Gazetteer (Claus et al., 2014) |GEBCO Gazetteer of Undersea Feature Names (IHO-IOC, https://www.ngdc.noaa.gov/gazetteer)</t>
+  </si>
+  <si>
+    <t>GEBCO Gazetteer of Undersea Feature Names (IHO-IOC, https://www.ngdc.noaa.gov/gazetteer)</t>
+  </si>
+  <si>
+    <t>asmr:standardGeographicFeatureValue</t>
+  </si>
+  <si>
+    <t>•	Marine Gazetteer (Claus et al., 2014), https://www.marineregions.org/gazetteer.php
+•	GEBCO Gazetteer of Undersea Feature Names (IHO-IOC, https://www.ngdc.noaa.gov/gazetteer)</t>
+  </si>
+  <si>
+    <t>Vercelli Seamount</t>
+  </si>
+  <si>
+    <t>asmr:verbatimLithology</t>
+  </si>
+  <si>
+    <t>The exposed granites of the peak, the terrace-like benches of the slopes and the organogenic sand on the plateau are considered consequences of the emersion, and subsequent subsidence, that the pinnacle experienced during the Pliocenic 130 meter glacial-eustatic decrease of the sea level [19], [30]. The seamount has been, and still is, subjected to tectonic movements accompanied by hydrothermal activity responsible for the iron-manganese crust (up to 2 cm thick) found on the deep granites [19].</t>
+  </si>
+  <si>
+    <t>asmr:verbatimGeomorphologicalContext</t>
+  </si>
+  <si>
+    <t>The geomorphological characteristics of the seamount have been studied by grabbing, dredging and underwater photoprofiling [19], [30]. These studies showed that the elevation arises from the muddy sea bottom with steep walls (about 20° slope) characterised by isolated granites and clay-limestone concretions emerging from the coarse detrital sand. Around 200–250 m depth, walls turn into flat planes covered by organogenic coarse and medium sand, gently sloping (1°–3° slope) up to about 100 m depth where a rocky peak rises reaching its maximal elevation around 60 m depth (Fig. 2a). This 2 miles elongated pinnacle (41°06.45′N–10°54.43′E, summit of the peak), represents the survey area. Here the bedrock takes the form of ridges separated by joints of various size and extent, traced by sandy sediments and running north eastward [19]. The two flanks of the pinnacle (NE and SW) show a different inclination being steeper on the SW side (17°30′) respect to the NE one (11°) [30].</t>
+  </si>
+  <si>
+    <t>Coastal and marine ecological classification standard (CMECS) (United States. Federal Geographic Data Committee and United States. National Ocean Service, 2012)</t>
+  </si>
+  <si>
+    <t>pinnacle seamount</t>
+  </si>
+  <si>
+    <t>fixed format</t>
+  </si>
+  <si>
+    <t>abyss</t>
+  </si>
+  <si>
+    <t>asmr:verbatimProtectionMeasures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any protection measures or restriction in place in the sampling sites as reported in text. </t>
+  </si>
+  <si>
+    <t>The Vercelli Seamount is not heavily exploited by professional fishing. Nevertheless, some abandoned nets and lines were observed along the ROV track. Environments characterised by high biodiversity should be worthy of protection by international conservation programs.</t>
+  </si>
+  <si>
+    <t>asmr:protectedAreaOrOECM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If applicable, protection level applying an appropriate classification scheme, e.g. the Classification System for Marine Protected Areas </t>
+  </si>
+  <si>
+    <t>https://www.classifympas.org/en/mpas-classification/</t>
+  </si>
+  <si>
+    <t>asmr:verbatimHabitat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Habitat as described in text. </t>
+  </si>
+  <si>
+    <t>Recommended best practice is to use a controlled vocabulary and separate multiple values in a list with space vertical bar space ( | )</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">coralligenous wall dominated by </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Paramuricea clavata</t>
+    </r>
+  </si>
+  <si>
+    <t>This pinnacle hosts a rich coralligenous community characterized by three different assemblages: (i) the top shows a dense covering of the kelp Laminaria rodriguezii; (ii) the southern side biocoenosis is mainly dominated by the octocorals Paramuricea clavata and Eunicella cavolinii; while (iii) the northern side of the seamount assemblage is colonized by active filter-feeding organisms such as sponges (sometimes covering 100% of the surface) with numerous colonies of the ascidian Diazona violacea, and the polychaete Sabella pavonina.</t>
+  </si>
+  <si>
+    <t>&lt;</t>
+  </si>
+  <si>
+    <t>asmr:habitatClassificationScheme</t>
+  </si>
+  <si>
+    <t>Habitat classification scheme used to specify asmr:standardHabitatValue, eco:targetHabitatScope, and eco:excludedHabitatScope</t>
+  </si>
+  <si>
+    <t>•	IUCN Global Ecosystem Typology (Keith et al., 2020)
+•	EUNIS (Davies et al., 2004)
+•	CATAMI (Althaus et al., 2015)
+•	NISB (Mount and Prahalad, 2010)
+•	CMECS graphic Data Committee and United States. National Ocean Service, 2012)
+•	Biomes listed in the Environment Ontology ENVO (Buttigieg et al., 2013)
+•	Interpretation Manual of Marine Habitat Types in the Mediterranean Sea (UNEP-MAP RAC/SPA, 2021)</t>
+  </si>
+  <si>
+    <t>Interpretation Manual of Marine Habitat Types in the Mediterranean Sea (UNEP-MAP RAC/SPA, 2021)</t>
+  </si>
+  <si>
+    <t>asmr:standardHabitatValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Habitat(s) present at the samplingSite according to asmr:habitatClassificationScheme. </t>
+  </si>
+  <si>
+    <t>MC1.514b Facies with Alcyonacea (e.g. Eunicella spp., Leptogorgia spp., Paramuricea spp., Corallium rubrum)</t>
+  </si>
+  <si>
+    <t>Coralligenous</t>
+  </si>
+  <si>
+    <t>asmr:standardFaciesValue</t>
+  </si>
+  <si>
+    <t>MC1.5 Circalittoral rock MC1.51 Coralligenous cliffs MC1.51a Algal-dominated coralligenous MC1.512a Association with Fucales or Laminariales | MC1.51b Invertebrate-dominated coralligenous | MC1.51b Invertebrate-dominated coralligenous Facies with large and erect sponges | MC1.514b Invertebrate-dominated coralligenous covered by sediment Facies with Alcyonacea</t>
+  </si>
+  <si>
+    <t>asmr:verbatimSubstrate</t>
+  </si>
+  <si>
+    <t>Substrate as described in text. Recommended best practice is to use a controlled vocabulary and separate multiple values in a list with space vertical bar space ( | )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This 2 miles elongated pinnacle (41°06.45′N–10°54.43′E, summit of the peak), represents the survey area. Here the bedrock takes the form of ridges separated by joints of various size and extent, traced by sandy sediments and running north eastward [19]. </t>
+  </si>
+  <si>
+    <t>asmr:standardSubstrateOrigin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substrate(s) present at the samplingSite according to asmr:substrateClassificationScheme. </t>
+  </si>
+  <si>
+    <t>•	Udden-Wentworth grain-size scale (Wentworth, 1922)
+•	Folk Triangle (Folk, 1954)
+•	EUNIS Modified Folk Triangle (Evans et al., 2016)
+•	CATAMI (Althaus et al., 2015)</t>
+  </si>
+  <si>
+    <t>Geologic | Biogenic</t>
+  </si>
+  <si>
+    <t>asmr:standardSubstrateClass</t>
+  </si>
+  <si>
+    <t>Rock substrate |  Algal Substrate</t>
+  </si>
+  <si>
+    <t>asmr:standardSubstrateSubclass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relevant only if asmr:standardSubstrateClass </t>
+  </si>
+  <si>
+    <t>Bedrock</t>
+  </si>
+  <si>
+    <t>asmr:standardSubstrateGroup</t>
+  </si>
+  <si>
+    <t>asmr:substrateClassificationScheme</t>
+  </si>
+  <si>
+    <t>Substrate classification scheme used to define asmr:standardSubstrate, asmr:substrateScope, asmr:excludedSubstrateScope</t>
+  </si>
+  <si>
+    <t>EUNIS Modified Folk Triangle (Evans et al., 2016)</t>
+  </si>
+  <si>
+    <t>Coastal and marine ecological classification standard (CMECS) Version 4 (United States. Federal Geographic Data Committee and United States. National Ocean Service, 2012)</t>
+  </si>
+  <si>
+    <t>Event</t>
+  </si>
+  <si>
+    <t>dwc:eventDate</t>
+  </si>
+  <si>
+    <t>The date and time of sampling, either as an instance (single point in time) or interval. Must follow ISO 8601 format (yyyy-mm-ddThh:mm:ss). Time zone must be specified after the timestamp (e.g., "2008-01-23T19:23-06:00" in the time zone six hours earlier than UTC, "2008-01-23T19:23Z" at UTC time). In case no exact time is available, the date/time can be right truncated i.e. all of these are valid times: 2008-01-23T19:23:10+00:00; 2008-01-23T19:23:10Z; 2008-01-23; 2008-01; 2008; Except: 2008-01; 2008 all are ISO8601 compliant. A date and time range can be specified using a forward slash (/) to separate the start and end values (e.g., 2008-01-23T19:23-06:00/2008-01-23T19:53-06:00). A duration can also be provided using the eventDurationValue term.</t>
+  </si>
+  <si>
+    <t>yyyy-mm-ddThh:mm:ss+-hh:mm</t>
+  </si>
+  <si>
+    <t>2008-01-23T19:23-06:00</t>
+  </si>
+  <si>
+    <t>DwC | MIxS</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/dwc/terms/eventDate | https://w3id.org/mixs/0000011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The duration of the sampling event, written in ISO 8601 format (i.e., P1DT3H for 1 day and 3 hours period. P1Y6M for 1 year and 6 months period. T30M/45M for some time between 30 and 45 minutes). </t>
+  </si>
+  <si>
+    <t>PnYnMnWnDTnHnMnS</t>
+  </si>
+  <si>
+    <t>T1H25M</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/eventDurationValue</t>
+  </si>
+  <si>
+    <t>The units associated with the eco:eventDurationValue.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Recommended best practice is to use a controlled vocabulary. This term has an equivalent in the ecoiri: namespace that allows only an IRI as a value, whereas this term allows for any string literal value.</t>
+  </si>
+  <si>
+    <t>minutes
+hours
+days
+months
+years</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/eventDurationUnit</t>
+  </si>
+  <si>
+    <t>dwc:verbatimEventDate</t>
+  </si>
+  <si>
+    <t>Sample collection date before formatting</t>
+  </si>
+  <si>
+    <t>23-January-2008</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/dwc/terms/verbatimEventDate</t>
+  </si>
+  <si>
+    <t>edna:verbatimEventTime</t>
+  </si>
+  <si>
+    <t>Sample collection time before formatting to ISO 8601, or at the local time (if eventDate time samp has been converted to UTC time)</t>
+  </si>
+  <si>
+    <t>10:23</t>
+  </si>
+  <si>
+    <t>Scope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The habitat targeted for sampling during the dwc:Event. </t>
+  </si>
+  <si>
+    <t>Separate the values in a list with space vertical bar space ( | ). This term has an equivalent in the ecoiri: namespace that allows only an IRI as a value, whereas this term allows for any string literal value.</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/targetHabitatScope</t>
+  </si>
+  <si>
+    <t>asmr:standardTargetHabitatScope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">habitat should be defined according to the asmr:habitatClassificationScheme. If no specific substrate, specify "No". </t>
+  </si>
+  <si>
+    <t>The habitats explicitly excluded from sampling during the dwc:Event.  If possible, habitat should be defined according to the asmr:habitatClassificationScheme</t>
+  </si>
+  <si>
+    <t>Separate multiple values in a list with space vertical bar space ( | ). If not defined in the sampling design, specify "No". This term has an equivalent in the ecoiri: namespace that allows only an IRI as a value, whereas this term allows for any string literal value.</t>
+  </si>
+  <si>
+    <t>Highly recommended</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/excludedHabitatScope</t>
+  </si>
+  <si>
+    <t>asmr:substrateScope</t>
+  </si>
+  <si>
+    <t>The substrate targeted for sampling during the dwc:Event defined according to the asmr:substrateClassificationScheme.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Separate multiple values in a list with space vertical bar space ( | ). If not defined in the sampling design, specify "No". </t>
+  </si>
+  <si>
+    <t>asmr:excludedSubstrateScope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The substrate(s) explicitly excluded from sampling during the dwc:Event  defined according to the asmr:substrateClassificationScheme. </t>
+  </si>
+  <si>
+    <t>The taxonomic group(s) targeted for sampling during the dwc:Event.</t>
+  </si>
+  <si>
+    <t>The dwc:Event to which the eco:targetTaxonomicScope refers could be at any level of hierarchy. In the case of a higher level (parent) dwc:Event, include all taxonomic groups surveyed in the child dwc:Events that contributed to the parent dwc:Event. Recommended best practice is to separate multiple values in a list with space vertical bar space ( | ). This term has an equivalent in the ecoiri: namespace that allows only an IRI as a value, whereas this term allows for any string literal value.</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/targetTaxonomicScope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	The taxonomic group(s) explicitly excluded from sampling during the dwc:Event.</t>
+  </si>
+  <si>
+    <t>The dwc:Event to which the eco:excludedTaxonomicScope refers could be at any level of hierarchy. In the case of a higher level (parent) dwc:Event, include all the taxonomic groups explicitly excluded from the child dwc:Events that contributed to the parent dwc:Event. Recommended best practice is to separate multiple values in a list with space vertical bar space ( | ). This term has an equivalent in the ecoiri: namespace that allows only an IRI as a value, whereas this term allows for any string literal value.</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/excludedTaxonomicScope</t>
+  </si>
+  <si>
+    <t>Statement about whether the taxonomic completeness of the dwc:Event was assessed.</t>
+  </si>
+  <si>
+    <t>This term is meant to alert users that the inventory was conducted in such a way that all of the target taxa (the combination of eco:targetTaxonomicScope and eco:excludedTaxonomicScope) should have been detectable if they were present during the dwc:Event. This term can provide data users with a qualitative measure of how comprehensively an area has been surveyed, which assists in interpreting species populations, areas of occupancy, inferring species absences, etc. This term is only relevant if the dwc:Event used restricted search or open search methods. If taxonomic completeness was assessed, the methods used or an explanation of the basis of the completeness should be stated in eco:taxonCompletenessProtocols. Recommended best practice is to use controlled value strings from the controlled vocabulary designated for use with this term, listed at http://rs.tdwg.org/dwc/doc/tcr/. This term has an equivalent in the ecoiri: namespace that allows only an IRI as a value, whereas this term allows for any string literal value.</t>
+  </si>
+  <si>
+    <t>Boolean</t>
+  </si>
+  <si>
+    <t>true / false</t>
+  </si>
+  <si>
+    <t>notReported
+reportedComplete
+reportedIncomplete</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/taxonCompletenessReported</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Every dwc:Organism that was included within the taxonomic scope, and was detected during the dwc:Event, was reported.</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/isTaxonomicScopeFullyReported</t>
+  </si>
+  <si>
+    <t>Taxonomic absences were reported.</t>
+  </si>
+  <si>
+    <t>Absences can be reported at any taxonomic level.</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/isAbsenceReported</t>
+  </si>
+  <si>
+    <t>A list (concatenated and separated) of taxa reported absent during the dwc:Event.</t>
+  </si>
+  <si>
+    <t>Absences can be reported at any taxonomic level. Recommended best practice is to separate multiple values in a list with space vertical bar space ( | ). This term has an equivalent in the ecoiri: namespace that allows only an IRI as a value, whereas this term allows for any string literal value.</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/absentTaxa</t>
+  </si>
+  <si>
+    <t>One or more dwc:Organisms of taxa outside the target taxonomic scope (the combination of eco:targetTaxonomicScope and eco:excludedTaxonomicScope) were detected and reported for this dwc:Event.</t>
+  </si>
+  <si>
+    <t>This term is meant to alert users to the presence of non-target taxa (in some disciplines called “bycatch”) reported in this dwc:Event. This term is relevant only if a target taxonomic scope is declared. Taxonomic scope is based on the combination of eco:targetTaxonomicScope and eco:excludedTaxonomicScope. Examination of the taxonomic scope is needed in order to identify the non-target taxa. It should be possible to confirm the expectations by investigating the dwc:Occurrences in this dwc:Event and in its child dwc:Events (if available) or by exploring eco:nonTargetTaxa for this dwc:Event (if populated). The value of this term should be 'true' if dwc:Occurrences of taxa outside the taxonomic scope as defined at the time of the dwc:Event are reported, otherwise the value of this term should be 'false'.</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/hasNonTargetTaxa</t>
+  </si>
+  <si>
+    <t>A list (concatenated and separated) of taxa reported during the dwc:Event that are outside of the target taxonomic scope (the combination of eco:targetTaxonomicScope and eco:excludedTaxonomicScope).</t>
+  </si>
+  <si>
+    <t>This term is meant to allow the full list of taxa that are considered outside of the taxonomic scope and yet were reported in the dataset to be shared. This term is relevant only if a target taxonomic scope is declared and eco:hasNonTargetTaxa is ‘true’. Taxonomic scope is based on the combination of eco:targetTaxonomicScope and eco:excludedTaxonomicScope. Non-target taxa (in some disciplines called “bycatch”) can be reported at any taxonomic level. Recommended best practice is to separate multiple values in a list with space vertical bar space ( | ). This term has an equivalent in the ecoiri: namespace that allows only an IRI as a value, whereas this term allows for any string literal value.</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/nonTargetTaxa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Every dwc:Organism that was outside of the target taxonomic scope (the combination of eco:targetTaxonomicScope and eco:excludedTaxonomicScope) and detected during the dwc:Event, and that was detectable using the given protocol (given in eco:protocolDescriptions and dwc:samplingProtocol), was reported.</t>
+  </si>
+  <si>
+    <t>This term is meant to inform a user of the data whether there were non-target taxa that were detected, but left unreported. This term is only relevant if the dwc:Event used restricted search or open search methods and if a target taxonomic scope is declared. Taxonomic scope is based on the combination of eco:targetTaxonomicScope and eco:excludedTaxonomicScope. Within dwc:Events that used either a restricted search or an open search method and declared a taxonomic scope, if all dwc:Organisms that are not included within the target taxonomic scope and that were detected during the dwc:Event were reported, the value of this term should be 'true', otherwise the value of this term should be ‘false'.</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/areNonTargetTaxaFullyReported</t>
+  </si>
+  <si>
+    <t>The age classes or life stages of the dwc:Organisms targeted for sampling during the dwc:Event.</t>
+  </si>
+  <si>
+    <t>This term is defined based on dwc:lifeStage (http://rs.tdwg.org/dwc/terms/lifeStage). Recommended best practice is to use the same controlled vocabulary as for dwc:lifeStage and to separate multiple values in a list with space vertical bar space ( | ). This term has an equivalent in the ecoiri: namespace that allows only an IRI as a value, whereas this term allows for any string literal value.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	
+larva
+adult | juvenile</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/targetLifeStageScope</t>
+  </si>
+  <si>
+    <t>The age classes or life stages of the dwc:Organisms explicitly excluded from sampling during the dwc:Event.</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/excludedLifeStageScope</t>
+  </si>
+  <si>
+    <t>Every dwc:Organism that was included within the life stage scope, and was detected during the dwc:Event, was reported.</t>
+  </si>
+  <si>
+    <t>This term is only relevant if the dwc:Event used restricted search or open search methods. If all dwc:Organisms included within the life stage scope and detected during the dwc:Event were reported, the value should be 'true'. Life stage scope is based on the combination of eco:targetLifeStageScope and eco:excludedLifeStageScope.</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/isLifeStageScopeFullyReported</t>
+  </si>
+  <si>
+    <t>The degrees of establishment of the dwc:Organisms targeted for sampling during the dwc:Event.</t>
+  </si>
+  <si>
+    <t>Recommended best practice is to use controlled value strings from the controlled vocabulary (http://rs.tdwg.org/dwcdoe/) for dwc:degreeOfEstablishment. For details, refer to https://doi.org/10.3897/biss.3.38084. Recommended best practice is to separate multiple values in a list with space vertical bar space ( | ). This term has an equivalent in the ecoiri: namespace that allows only an IRI as a value, whereas this term allows for any string literal value.</t>
+  </si>
+  <si>
+    <t>native
+invasive | widespreadInvasive</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/targetDegreeOfEstablishmentScope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	The degrees of establishment of the dwc:Organisms explicitly excluded from sampling during the dwc:Event.</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/excludedDegreeOfEstablishmentScope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Every dwc:Organism that was included within the degree of establishment scope, and was detected during the dwc:Event, was reported.</t>
+  </si>
+  <si>
+    <t>This term is only relevant if the dwc:Event used restricted search or open search methods. If all dwc:Organisms included within the degree of establishment scope and detected during the dwc:Event were reported, the value should be 'true'. Degree of establishment scope is based on the combination of eco:targetDegreeOfEstablishmentScope and eco:excludedDegreeOfEstablishmentScope.</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/isDegreeOfEstablishmentScopeFullyReported</t>
+  </si>
+  <si>
+    <t>The growth forms or habits of the dwc:Organisms targeted for sampling during the dwc:Event.</t>
+  </si>
+  <si>
+    <t>Recommended best practice is to use a controlled vocabulary and separate multiple values in a list with space vertical bar space ( | ). This term has an equivalent in the ecoiri: namespace that allows only an IRI as a value, whereas this term allows for any string literal value.</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/targetGrowthFormScope</t>
+  </si>
+  <si>
+    <t>The growth forms or habits of the dwc:Organisms explicitly excluded from sampling during the dwc:Event.</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/excludedGrowthFormScope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Every dwc:Organism that was included within the growth form scope, and was detected during the dwc:Event, was reported.</t>
+  </si>
+  <si>
+    <t>This term is only relevant if the dwc:Event used restricted search or open search methods. If all dwc:Organisms included within the growth form scope and detected during the dwc:Event were reported, the value should be 'true'. Growth form scope is based on the combination of eco:targetGrowthFormScope and eco:excludedGrowthFormScope.</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/isGrowthFormScopeFullyReported</t>
+  </si>
+  <si>
+    <t>One or more dwc:Organisms outside the target organismal scopes (eco:targetDegreeOfEstablishmentScope, eco:targetGrowthFormScope, and eco:targetLifeStageScope) were detected and reported for this dwc:Event.</t>
+  </si>
+  <si>
+    <t>This term is meant to alert users to the presence of non-target organisms (in some disciplines called “bycatch”) reported in this dwc:Event. This term is relevant only if a target organismal scope is declared. Organismal scope is based on the combination of all of the following terms: eco:targetLifeStageScope, eco:excludedLifeStageScope, eco:targetDegreeOfEstablishmentScope, eco:excludedDegreeOfEstablishmentScope, eco:targetGrowthFormScope, and eco:excludedGrowthFormScope. Examination of the organismal scope is needed in order to identify the non-target dwc:Organisms. It should be possible to confirm the expectations by investigating the dwc:Occurrences in this dwc:Event and in its child dwc:Events (if available). The value of this term should be 'true' if dwc:Occurrences of dwc:Organisms outside the organismal scope(s) as defined at the time of the dwc:Event are reported, otherwise the value of this term should be 'false'.</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/hasNonTargetOrganisms</t>
+  </si>
+  <si>
+    <t>The verbatim original description of the dwc:Event scope.</t>
+  </si>
+  <si>
+    <t>Recommended best practice is first to populate explicit scope terms to the fullest extent possible (e.g., eco:targetTaxonomicScope). It is not recommended to use this term in assessing absence or completeness.</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/verbatimTargetScope</t>
+  </si>
+  <si>
+    <t>methodsMetadata</t>
+  </si>
+  <si>
+    <t>Sampling materials</t>
+  </si>
+  <si>
+    <t>asmr:samplingPlatform</t>
+  </si>
+  <si>
+    <t>Observation-class ROV | dredge</t>
+  </si>
+  <si>
+    <t>asmr:samplingPlatformModel</t>
+  </si>
+  <si>
+    <t>Model of the samplign platform adopted for fieldwork. Separate multiple values in a list with space vertical bar space ( | )</t>
+  </si>
+  <si>
+    <t>Ocean Robotics Njord ROV</t>
+  </si>
+  <si>
+    <t>ROV Pluto (Gaymarine, Switzerland) | dredging (dredge mouth 60 cm in diameter)</t>
+  </si>
+  <si>
+    <t>asmr:divingGasMix</t>
+  </si>
+  <si>
+    <t>If asmr:samplingPlatform included "open-circuit SCUBA" or "close-circuit rebreathers" or "semi-closed rebreathers" specify the diving gas mix, if necessary differentiating between bottom and decompression gases</t>
+  </si>
+  <si>
+    <t>Platform-specific</t>
+  </si>
+  <si>
+    <t>Relevant if asmr:samplingPlatform includes diving</t>
+  </si>
+  <si>
+    <t>Bottom gas Trimix 21/35 | Decompression gas O50</t>
+  </si>
+  <si>
+    <t>asmr:positioningSystem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System for the tracking and navigation of underwater vehicles or divers by means of acoustic distance and/or direction measurements, and subsequent position triangulation. </t>
+  </si>
+  <si>
+    <t>Blueprint SeaTrac USBL Positioning System</t>
+  </si>
+  <si>
+    <t>underwater acoustic tracking position system (HDR made by Gaymarine ultrashort baseline operating with a 30 kHz responder)</t>
+  </si>
+  <si>
+    <t>ifdo:image-scale-reference</t>
+  </si>
+  <si>
+    <t>3D camera: the imaging system provides scale directly, calibrated camera: image data and additional external data like object distance provide scale together, laser marker: scale information is embedded in the visual data, optical flow: scale is computed from the relative movement of the images and the camera navigation data</t>
+  </si>
+  <si>
+    <t>3D camera, calibrated camera, laser marker, optical flow</t>
+  </si>
+  <si>
+    <t>IFDO</t>
+  </si>
+  <si>
+    <t>laser marker</t>
+  </si>
+  <si>
+    <t>asmr:sizeReferenceSystem</t>
+  </si>
+  <si>
+    <t>Size reference system is used for size estimation in visual-based surveys</t>
+  </si>
+  <si>
+    <t>Relevant for visual-based platforms if samples include photos / videos</t>
+  </si>
+  <si>
+    <t>2 green laser beams (OrcaTorch D560-GL) set 10 cm apart</t>
+  </si>
+  <si>
+    <t>two parallel laser beams (90° angle) providing a 10 cm scale for measuring the areas of the frames</t>
+  </si>
+  <si>
+    <t>asmr:lightSystem</t>
+  </si>
+  <si>
+    <t>Separate multiple values in a list with space vertical bar space ( | )</t>
+  </si>
+  <si>
+    <t>asmr:cameraSystem</t>
+  </si>
+  <si>
+    <t>Model of the camera(s) used for eco:protocolDescriptions</t>
+  </si>
+  <si>
+    <t>Olympus Tough! TG6 with Isotta underwater housing</t>
+  </si>
+  <si>
+    <t>digital camera Nikon Coolpix 8700  | video camera (Sony DV 3CCD mod 950)</t>
+  </si>
+  <si>
+    <t>durden:image-camera-orientation*</t>
+  </si>
+  <si>
+    <t>Inclination of the camera with respect to the substrate expressed in degrees, e.g. if perpendicular,  fill"90"</t>
+  </si>
+  <si>
+    <t>asmr:batterySystem</t>
+  </si>
+  <si>
+    <t>Battery system adopted for the sampling platform</t>
+  </si>
+  <si>
+    <t>asmr:sensors</t>
+  </si>
+  <si>
+    <t>Specify sensor(s) the sampling platform is equipped with or that have been used in the sampling design. Recommended best practice is to use a controlled vocabulary and separate multiple values in a list with space vertical bar space ( | )</t>
+  </si>
+  <si>
+    <t>CTD | light sensors</t>
+  </si>
+  <si>
+    <t>depth sensor | compass</t>
+  </si>
+  <si>
+    <t>asmr:sensorsCalibration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protocol adopted for sensor calibration. Refer to the manual / source if available. </t>
+  </si>
+  <si>
+    <t>asmr:pelagicORbenthicBaitedPlatform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If a baited platform is adopted, specify whether it is a pelagic or benthic platform. </t>
+  </si>
+  <si>
+    <t>restricted</t>
+  </si>
+  <si>
+    <t>"pelagic" OR "benthic"</t>
+  </si>
+  <si>
+    <t>asmr:bait</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bait equipped to the baited platform. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required if asmr:samplingPlatform is baited </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>chopped European sardine</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Sardina pilchardus</t>
+    </r>
+  </si>
+  <si>
+    <t>asmr:baitQuantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity of the bait equipped to the baited platform expressed in kg. </t>
+  </si>
+  <si>
+    <t>asmr:manipulatorArms</t>
+  </si>
+  <si>
+    <t>Specify if the sampling platform is equipped with manipulator arms for manipulative experiments or sample collection. If absent, set "No".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only relevant if asmr:samplingPlatform is baited </t>
+  </si>
+  <si>
+    <t>boolean</t>
+  </si>
+  <si>
+    <t>asmr:sampleContainer</t>
+  </si>
+  <si>
+    <t>Specify if the sampling platform is equipped with a sample container, e.g. voucher specimens container for ROVs. If absent, set "No".</t>
+  </si>
+  <si>
+    <t>asmr:otherFaunaAttraction</t>
+  </si>
+  <si>
+    <t>Specify if any other fauna attraction device/tool was equiped to the baited platform. If absent, mark "No".</t>
+  </si>
+  <si>
+    <t>asmr:armLength</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baited platform arm length in m. </t>
+  </si>
+  <si>
+    <t>asmr:canisterModel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model of the canister of the baited platform. </t>
+  </si>
+  <si>
+    <t>Sampling Design</t>
+  </si>
+  <si>
+    <t>asmr:surveyType</t>
+  </si>
+  <si>
+    <t>incidental data | elementary inventory | extended inventory | compilation</t>
+  </si>
+  <si>
+    <t>Sica et al., 2026</t>
+  </si>
+  <si>
+    <t>extended inventory</t>
+  </si>
+  <si>
+    <t>A statement specifying whether data reported are derived from sampling events, ancillary data compiled from other sources, or a combination of both.</t>
+  </si>
+  <si>
+    <t>This term is only relevant if the dwc:Event is an inventory. Recommended best practice is to use a controlled vocabulary. Recommended best practice is to separate the values in a list with space vertical bar space ( | ). This term has an equivalent in the ecoiri: namespace that allows only an IRI as a value, whereas this term allows for any string literal value.</t>
+  </si>
+  <si>
+    <t>Only relevant if the dwc:Event is an inventory</t>
+  </si>
+  <si>
+    <t>samplingEvents
+compilationOfExistingSourcesAndSamplingEvents
+compilationOfExistingSources
+compilationOfExistingSourcesAndSamplingEvents | compilationOfExistingSources</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/compilationTypes</t>
+  </si>
+  <si>
+    <t>The types of data sources contributing to the compilation reported.</t>
+  </si>
+  <si>
+    <t>This term is only relevant if the dwc:Event is a compilation in which one or more types of data sources were used. Recommended best practice is to use a controlled vocabulary and separate multiple values in a list with space vertical bar space ( | ). This term has an equivalent in the ecoiri: namespace that allows only an IRI as a value, whereas this term allows for any string literal value.</t>
+  </si>
+  <si>
+    <t>Only relevant if the dwc:Event is an compilation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	
+museumSpecimens
+literature
+expertKnowledge | localKnowledge  | web knowledge</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/compilationSourceTypes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	The types of search processes used to conduct the inventory.</t>
+  </si>
+  <si>
+    <t>This term is only relevant if the dwc:Event represents an inventory. Recommended best practice is to use a controlled vocabulary. Recommended best practice is to separate multiple values in a list with space vertical bar space ( | ). This term has an equivalent in the ecoiri: namespace that allows only an IRI as a value, whereas this term allows for any string literal value.</t>
+  </si>
+  <si>
+    <t>restrictedSearch
+openSearch
+opportunisticSearch
+adventitious
+compilation
+openSearch | opportunisticSearch</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/inventoryTypes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	The number of dwc:Organisms collected or observed was reported.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Typically the abundance values would be reported in the dwc:organismQuantity and dwc:organismQuantityType terms for the child dwc:Occurrence records for this dwc:Event.</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/isAbundanceReported</t>
+  </si>
+  <si>
+    <t xml:space="preserve">semiquantitative </t>
+  </si>
+  <si>
+    <t>A maximum number of dwc:Organisms was reported, as specified or restricted by the protocol used.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Values of abundance cap should be captured under the term eco:abundanceCap.</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/isAbundanceCapReported</t>
+  </si>
+  <si>
+    <t>The reported maximum number of dwc:Organisms.</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/abundanceCap</t>
+  </si>
+  <si>
+    <t>The total detected quantity for a dwc:Taxon (including subcategories thereof) in a dwc:Event is given explicitly in a single record (dwc:organismQuantity value) for that dwc:Taxon.</t>
+  </si>
+  <si>
+    <t>Recommended values are 'true' and 'false'. This term is only relevant if dwc:organismQuantity is a number. For a detailed explanation, see http://rs.tdwg.org/dwc/doc/inclusive/.</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/isLeastSpecificTargetCategoryQuantityInclusive</t>
+  </si>
+  <si>
+    <t>The sampling effort associated with the dwc:Event was reported.</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/isSamplingEffortReported</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The numeric value for the sampling effort expended during the dwc:Event. </t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/samplingEffortValue</t>
+  </si>
+  <si>
+    <t>The units associated with the eco:samplingEffortValue. Sampling unit can be expressed in terms of surface, e.g. for transects, or soaking time for stationary platforms.</t>
+  </si>
+  <si>
+    <t>Linear transect</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/samplingEffortUnit</t>
+  </si>
+  <si>
+    <t>A description of or reference (publication or URL) to the methods used to determine the sampling effort.</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/samplingEffortProtocol</t>
+  </si>
+  <si>
+    <t>asmr:excludedSamplingEffortUnit</t>
+  </si>
+  <si>
+    <t>Number of sampling unit excluded from analysis.</t>
+  </si>
+  <si>
+    <t>Megabenthos and ichtyopfauna was compiled from photos, dredged material, and complete videotransects. Target taxa density only from subsampled video frames.</t>
+  </si>
+  <si>
+    <t>asmr:excludedSamplingEffortUnitRationale</t>
+  </si>
+  <si>
+    <t>If any sample was excluded, explain the rationale, e.g. blurred photo or specimen with head structures.</t>
+  </si>
+  <si>
+    <t>The density (in terms of specimens or colonies m−2) or covering (% estimation) of 11 conspicuous and recognizable megabenthic species (or species groups) were evaluated on 14 video frames randomly obtained for each video-transect, for a total of 98 frames.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Categorical descriptive names for the methods used during the dwc:Event.</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/protocolNames</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	A detailed description of the methods used during the dwc:Event.</t>
+  </si>
+  <si>
+    <t>This description should be associated with protocols provided in eco:protocolNames. The description may include deviations from a protocol referred to in eco:protocolReferences. Recommended good practice is to provide information about instruments used, calibration, etc. Recommended best practice is to separate multiple values in a list with space vertical bar space ( | ).</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/protocolDescriptions</t>
+  </si>
+  <si>
+    <t>The references to the methods used during the dwc:Event.</t>
+  </si>
+  <si>
+    <t>Recommended best practice is to separate multiple values in a list with space vertical bar space ( | ).</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/protocolReferences</t>
+  </si>
+  <si>
+    <t>asmr:validationProtocolDescription</t>
+  </si>
+  <si>
+    <t>A detailed description of any validation protocol adopted to reduce measurements biases.</t>
+  </si>
+  <si>
+    <t>the footage was analyzed twice by two researchers and results were compared reaching consensus on the ones here presented.</t>
+  </si>
+  <si>
+    <t>To confirm the taxonomic determination of the specimens counted in the frames, we examined samples collected by dredging (dredge mouth 60 cm in diameter) on the seamount (60–100 m depth) during an oceanographic campaign on board of the R/V Urania in May 2009. A more complete list of the recorded species (and their relative abundance) (Table 1) was obtained both by the analysis of the dredged samples and the examination of the whole video and photographic material.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Site refers to the location at which observations are made or samples/measurements are taken. The site can be at any level of hierarchy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Textual description of the hierarchical sampling design. </t>
+  </si>
+  <si>
+    <t>Site refers to the location at which observations are made or samples/measurements are taken. The site can be at any level of hierarchy. If sites are not nested, set "No"</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/siteNestingDescription</t>
+  </si>
+  <si>
+    <t>Original textual description of the site(s).
+Comments: Site refers to the location at which observations are made or samples/measurements are taken. The site can be at any level of hierarchy. Recommended best practice is to separate multiple values in a list with space vertical bar space ( | ).</t>
+  </si>
+  <si>
+    <t>A list (concatenated and separated) of original site names.
+Comments: Site refers to the location at which observations are made or samples/measurements are taken. The site can be at any level of hierarchy. Recommended best practice is to separate multiple values in a list with space vertical bar space ( | ).</t>
+  </si>
+  <si>
+    <t>A description of or reference (publication, URL) to the methods used to determine eco:taxonCompletenessReported.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	This term allows users to determine how comprehensively an area has been sampled. Recommended best practice is to separate multiple values in a list with space vertical bar space ( | ). This term has an equivalent in the ecoiri: namespace that allows only an IRI as a value, whereas this term allows for any string literal value.</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/iri/taxonCompletenessProtocols</t>
+  </si>
+  <si>
+    <t>The numeric value for the total area surveyed during the dwc:Event.</t>
+  </si>
+  <si>
+    <t>This area is always less than or equal to the eco:geospatialScopeAreaValue. An eco:totalAreaSampledValue must have a corresponding eco:totalAreaSampledUnit.</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/totalAreaSampledValue</t>
+  </si>
+  <si>
+    <t>The units associated with eco:totalAreaSampledValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Recommended best practice is to use a controlled vocabulary. For units containing exponents, use characters from the Unicode Latin-1 Supplement character set (hex 00B2 for squared and 00B3 for cubed). This term has an equivalent in the ecoiri: namespace that allows only an IRI as a value, whereas this term allows for any string literal value.</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/totalAreaSampledUnit</t>
+  </si>
+  <si>
+    <t>asmr:analyzedAreaValue</t>
+  </si>
+  <si>
+    <t>The numeric value of the area included for quantitative analysis that can be equal to or a subset of the total area surveyed during the dwc:Event.</t>
+  </si>
+  <si>
+    <t>asmr:analyzedAreaUnit</t>
+  </si>
+  <si>
+    <t>The units associated with asmr:analyzedAreaValue</t>
+  </si>
+  <si>
+    <t>asmr:fieldOfView</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For visual-based survey, field of view of the platform expressed in m^2. </t>
+  </si>
+  <si>
+    <t>asmr:navigationSpeed</t>
+  </si>
+  <si>
+    <t>Platform navigation speed expressed in m/s</t>
+  </si>
+  <si>
+    <t>A list of weather or climatic conditions present during the dwc:Event.</t>
+  </si>
+  <si>
+    <t>Recommended best practice is to use a key:value encoding schema for a data interchange format such as JSON.</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/reportedWeather</t>
+  </si>
+  <si>
+    <t>A description of any extreme weather or environmental conditions that may have affected the dwc:Event.</t>
+  </si>
+  <si>
+    <t>flooding during week 3 of surveys
+rockslide at site 2</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/reportedExtremeConditions</t>
+  </si>
+  <si>
+    <t>asmr:spatialReplicates</t>
+  </si>
+  <si>
+    <t>true or false</t>
+  </si>
+  <si>
+    <t>14 video frames randomly obtained for each video-transect</t>
+  </si>
+  <si>
+    <t>asmr:temporalReplicates</t>
+  </si>
+  <si>
+    <t>asmr:temporalScale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If asmr:temporalReplicates = true, specify the time span in years. </t>
+  </si>
+  <si>
+    <t>asmr:minimumSurveyedDepth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum surveyed depth expressed in metres </t>
+  </si>
+  <si>
+    <t>asmr:maximumSurveyedDepth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximum surveyed depth expressed in metres </t>
+  </si>
+  <si>
+    <t>asmr:minimumAnalyzedDepth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum surveyed depth whose samples were included in descriptive or quantitative analyses expressed in metres </t>
+  </si>
+  <si>
+    <t>asmr:maximumAnalyzedDepth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximum surveyed depth whose samples were included in descriptive or quantitative analyses expressed in metres </t>
+  </si>
+  <si>
+    <t>asmr:surveyedTime</t>
+  </si>
+  <si>
+    <t>Time for samplingEffortUnit, e.g. navigation for time-based transect or soak time for stationary sampling platforms) expressed in minutes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For baited platforms, surveyedTime should include both the settling time after deployment and the analyzedTime.  </t>
+  </si>
+  <si>
+    <t>asmr:analyzedTime</t>
+  </si>
+  <si>
+    <t>Time subset of asmr:surveyedTime that was included in descriptive or quantitative analyses expressed in minutes.</t>
+  </si>
+  <si>
+    <t>dwc:maximumDistanceAboveSurfaceInMeters</t>
+  </si>
+  <si>
+    <t>The greater distance in a range of distance from a reference surface in the vertical direction, in meters. Use positive values for locations above the surface, negative values for locations below. If depth measures are given, the reference surface is the location given by the depth, otherwise the reference surface is the location given by the elevation.</t>
+  </si>
+  <si>
+    <t>Example:For a 1.5 meter sediment core from the bottom of a lake (at depth 20m) at 300m elevation: verbatimElevation: 300m minimumElevationInMeters: 300, maximumElevationInMeters: 300, verbatimDepth: 20m, minimumDepthInMeters: 20, maximumDepthInMeters: 20, minimumDistanceAboveSurfaceInMeters: 0, maximumDistanceAboveSurfaceInMeters: -1.5.</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/dwc/terms/maximumDistanceAboveSurfaceInMeters</t>
+  </si>
+  <si>
+    <t>Risk assessment and prevention measures</t>
+  </si>
+  <si>
+    <t>asmr:protocolRisks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risks related to the protocol described in eco:protocolDescriptions </t>
+  </si>
+  <si>
+    <t>asmr:protocolPreventionMeasures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any prevention measure against the risk specified in asmr:protocolRisks associated with the sampling protocol described in eco:protocolDescriptions </t>
+  </si>
+  <si>
+    <t>Cost analysis</t>
+  </si>
+  <si>
+    <t>asmr:costPerCostAnalysisUnit</t>
+  </si>
+  <si>
+    <t>Cost expressed in asmr:costAnalysisCurrency per asmr:costAnalysisUnit</t>
+  </si>
+  <si>
+    <t>asmr:costAnalysisCurrency</t>
+  </si>
+  <si>
+    <t>Currency used to express asmr:costPerUnit, asmr:equipmentCostPerUnit, and asmr:personnelCostPerUnit</t>
+  </si>
+  <si>
+    <t>asmr:costAnalysisUnit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Define a unit for the cost analysis of the described eco:protocolDescriptions </t>
+  </si>
+  <si>
+    <t>m^2 ; per transplant; per site</t>
+  </si>
+  <si>
+    <t>asmr:personnelCostPerUnit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personnel cost per unit as specified in asmr:costAnalysisUnit expressed in asmr:costAnalysisCurrency </t>
+  </si>
+  <si>
+    <t>asmr:equipmentCostPerUnit</t>
+  </si>
+  <si>
+    <t>Equipment cost per unit as specified in asmr:costAnalysisUnit expressed in asmr:costAnalysisCurrency.</t>
+  </si>
+  <si>
+    <t>Material collected</t>
+  </si>
+  <si>
+    <t>Specimen vouchers were collected during the dwc:Event.</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/hasVouchers</t>
+  </si>
+  <si>
+    <t>A list (concatenated and separated) of the names or acronyms of the institutions where vouchers collected during the dwc:Event were deposited.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Recommended best practice is to separate multiple values in a list with space vertical bar space ( | ).</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/voucherInstitutions</t>
+  </si>
+  <si>
+    <t>Material samples were collected during the dwc:Event.</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/hasMaterialSamples</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/eco/terms/materialSampleTypes</t>
+  </si>
+  <si>
+    <t>Sample collection</t>
+  </si>
+  <si>
+    <t>edna:biological_rep</t>
+  </si>
+  <si>
+    <t>The number of biological replicates collected at each sampling point and/or for each experimental treatment in the study.</t>
+  </si>
+  <si>
+    <t>integer</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Digital sample</t>
+  </si>
+  <si>
+    <t>ifdo:image-area-square-meters</t>
+  </si>
+  <si>
+    <t>0.5-3 (mean 1.75)</t>
+  </si>
+  <si>
+    <t>ifdo:image-resolution</t>
+  </si>
+  <si>
+    <t>ifdo:image-overlap-fraction</t>
+  </si>
+  <si>
+    <t>ifdo:image-science-use-cases</t>
+  </si>
+  <si>
+    <t>ifdo:image-camera-calibration-model</t>
+  </si>
+  <si>
+    <t>ifdo:image-item-identification-scheme</t>
+  </si>
+  <si>
+    <t>ifdo:image-curation-protocol</t>
+  </si>
+  <si>
+    <t>Details of image processing / curation applied. References required should be listed in image-documentation-processing</t>
+  </si>
+  <si>
+    <t>ifdo:image-photometric-calibration</t>
+  </si>
+  <si>
+    <t>Sample relations</t>
+  </si>
+  <si>
+    <t>dwc:materialSampleID</t>
+  </si>
+  <si>
+    <t>An identifier for the physical sample (as opposed to the extracted DNA sample defined by samp_name). In the absence of a persistent global unique identifier, construct one from a combination of identifiers in the record.</t>
+  </si>
+  <si>
+    <t>GOMECC4_27N_Sta1_Deep</t>
+  </si>
+  <si>
+    <t>http://rs.tdwg.org/dwc/terms/materialSampleID</t>
+  </si>
+  <si>
+    <t>Not provided</t>
+  </si>
+  <si>
+    <t>representation of real world phenomenon associated with a location relative to the Earth</t>
+  </si>
+  <si>
+    <t>asmr:physiographicContext</t>
+  </si>
+  <si>
+    <t>Physiographical features as defined by the  ISGM Physiography vocabulary</t>
+  </si>
+  <si>
+    <t>continental slope
+continental rise
+abyssal plain
+accretionary prism
+axial high
+axial valley
+back-arc basin
+continental shelf
+fore-arc basin
+island arc
+mid-ocean ridge
+oceanic trench
++ hadal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISGM Seabed geomorphology - Physiography Vocabulary https://pid.geoscience.gov.au/def/voc/ga/SeabedGeomorphologyPhysiography </t>
+  </si>
+  <si>
+    <t>continental shelf</t>
+  </si>
+  <si>
+    <t>Recommended best practice is to use ISGM Seabed geomorphology - Part 2 Geomorphology and separate multiple values in a list with space vertical bar space ( | ).</t>
+  </si>
+  <si>
+    <t>ISGM Seabed geomorphology - Part 1 Morphology Vocabulary https://pid.geoscience.gov.au/def/voc/ga/SeabedGeomorphologyMorphology | Coastal and marine ecological classification standard (CMECS) (United States. Federal Geographic Data Committee and United States. National Ocean Service, 2012)</t>
+  </si>
+  <si>
+    <t>Major geomorphic and structural characteristics of the coast and seafloor</t>
+  </si>
+  <si>
+    <t>asmr:geomorphologyClassificationScheme</t>
+  </si>
+  <si>
+    <t>asmr:geomorphologicalContext</t>
+  </si>
+  <si>
+    <t>Classification scheme used to define asmr:geomorphologicalContext, asmr:physiographicContext</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISGM Seabed geomorphology - Part 1 Morphology Vocabulary https://pid.geoscience.gov.au/def/voc/ga/SeabedGeomorphologyMorphology </t>
+  </si>
+  <si>
+    <t>Relevant only if asmr:geomorphologicalContext, asmr:physiographicContext are compiled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Origin of the substrate(s) present at the samplingSite according to asmr:substrateClassificationScheme. </t>
+  </si>
+  <si>
+    <t>Geologic | Biogenic | Artificial</t>
+  </si>
+  <si>
+    <t>Physical person or device/machine conducting fieldwork sampling</t>
+  </si>
+  <si>
+    <t>asmr:inSituAbioticParametersCollected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recommended best practice is to use a controlled vocabulary and to separate multiple values in a list with space vertical bar space ( | ). If using NETMAR Oceanography Thesaurus Parameter Facet, use first level concept hierarchy. </t>
+  </si>
+  <si>
+    <t>NETMAR Oceanography Thesaurus Parameter Facet  http://vocab.nerc.ac.uk/scheme/NETOC_PARAM/current/</t>
+  </si>
+  <si>
+    <t>Water temperature</t>
+  </si>
+  <si>
+    <t>Chlorophyll-a concentration | Turbidity</t>
+  </si>
+  <si>
+    <t>asmr:inSituAbioticlParametersAnalyzed</t>
+  </si>
+  <si>
+    <t>asmr:exSituAbioticParametersAnalyzed</t>
+  </si>
+  <si>
+    <t>asmr:ecologicalParameters</t>
+  </si>
+  <si>
+    <t>171.5  | 1400</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.5 m^2 corresponds to the subset of video frames analyzed for SS | 1400 m^2 to the whole videotransects analyzed for megabenthos diversity </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> If different area were analyzed for different puroposes, separate multiple values in a list with space vertical bar space ( | ) and specify to what each area value corresponds in the Notes. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boolean field to specify whether spatial repliactes were included in the sampling design (e.g. multiple transects or photquadrats) </t>
+  </si>
+  <si>
+    <t>Boolean field to specify whether temporal replicates were included in the sampling design</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Abiotic parameters collected </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>in situ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> during fieldwork.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Abiotic parameters collected </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ex situ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and included in analyses (e.g. satellite-derived data)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Abiotic parameters collected </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">in situ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>during fieldwork and included in analyses (e.g. satellite-derived data)</t>
+    </r>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>P/A | individual / colony density</t>
+  </si>
+  <si>
+    <t>Parameters</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -915,17 +2810,130 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBB4AE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3CDE3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFED9A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDECBE4"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -941,7 +2949,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -962,6 +2970,88 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1305,6 +3395,23 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="P62" dT="2026-04-15T13:30:03.51" personId="{06DEABF6-2585-4535-81B1-D5EA4F836F3B}" id="{BBEAE2E5-2B03-43BD-B0A8-9BC6843E9ADC}">
+    <text>Check humboldt use case</text>
+  </threadedComment>
+  <threadedComment ref="P86" dT="2026-04-15T12:51:38.30" personId="{06DEABF6-2585-4535-81B1-D5EA4F836F3B}" id="{88C3F7A2-0849-4EAC-9403-E876BF64BDD2}">
+    <text>Same as model?</text>
+  </threadedComment>
+  <threadedComment ref="P103" dT="2026-04-15T16:07:22.32" personId="{06DEABF6-2585-4535-81B1-D5EA4F836F3B}" id="{3B269ACA-71E5-4733-9E6C-3A5752A3F20B}">
+    <text>Definition!?</text>
+  </threadedComment>
+  <threadedComment ref="P122" dT="2026-04-15T13:36:06.03" personId="{06DEABF6-2585-4535-81B1-D5EA4F836F3B}" id="{B72C3B60-DE4A-428A-842F-0321C07BC243}">
+    <text>HUMBOLDT USE CASE</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="M2" dT="2026-04-15T13:30:03.51" personId="{06DEABF6-2585-4535-81B1-D5EA4F836F3B}" id="{F778C68F-B3AA-49A7-8F4C-181180D98A3B}">
     <text>Check humboldt use case</text>
   </threadedComment>
@@ -1318,179 +3425,5210 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A929A264-79BF-4A80-8B48-FBF349CD37CB}">
-  <dimension ref="A1:T3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6B7A37C-4894-4CC6-96F9-8A445DB3D3C0}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:Q165"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.21875" customWidth="1"/>
-    <col min="2" max="2" width="19.109375" customWidth="1"/>
-    <col min="4" max="4" width="15.33203125" customWidth="1"/>
-    <col min="13" max="13" width="24.109375" customWidth="1"/>
+    <col min="1" max="1" width="18" style="11" customWidth="1"/>
+    <col min="2" max="2" width="17.21875" style="11" customWidth="1"/>
+    <col min="3" max="3" width="45.33203125" style="27" customWidth="1"/>
+    <col min="4" max="4" width="45.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="74.77734375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="19.33203125" style="11" customWidth="1"/>
+    <col min="7" max="7" width="26" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.77734375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" style="11"/>
+    <col min="10" max="10" width="18.21875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="39.109375" style="2" customWidth="1"/>
+    <col min="12" max="12" width="30.88671875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="24.6640625" style="11" customWidth="1"/>
+    <col min="14" max="14" width="61.6640625" style="11" customWidth="1"/>
+    <col min="15" max="15" width="39.33203125" style="11" customWidth="1"/>
+    <col min="16" max="16" width="86.44140625" style="2" customWidth="1"/>
+    <col min="17" max="17" width="35.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="N2" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="N3" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="O3" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="P3" s="15" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="N4" s="2"/>
+      <c r="P4" s="15" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="N5" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="N6" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="N7" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="N8" s="2"/>
+      <c r="P8" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="N9" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="N10" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="N11" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="N12" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="N13" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="O13" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="N14" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="P14" s="6" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="O15" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L16" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="P16" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="N17" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="O17" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="P17" s="2">
+        <v>10.907166999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="N18" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="O18" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="P18" s="2">
+        <v>41.107500000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="N19" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="O19" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="N20" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="O20" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="N21" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="O21" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="M22" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="N22" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="O22" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="17"/>
+      <c r="C23" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N23" s="18" t="s">
+        <v>292</v>
+      </c>
+      <c r="P23" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="17"/>
+      <c r="C24" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="M24" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N24" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="17"/>
+      <c r="C25" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="F25" s="14"/>
+      <c r="M25" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N25" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="17"/>
+      <c r="C26" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="F26" s="14"/>
+      <c r="M26" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N26" s="18" t="s">
+        <v>301</v>
+      </c>
+      <c r="P26" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" ht="108" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="17"/>
+      <c r="C27" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="F27" s="14"/>
+      <c r="M27" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N27" s="18" t="s">
+        <v>304</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="102" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>305</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="M28" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="P28" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B29" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="M29" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="P29" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B30" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>313</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="L30" s="2">
+        <v>25035</v>
+      </c>
+      <c r="M30" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="P30" s="2">
+        <v>25035</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+      <c r="B31" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>315</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F31" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="M31" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="P31" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+      <c r="B32" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="D32" s="20" t="s">
+        <v>690</v>
+      </c>
+      <c r="E32" s="20"/>
+      <c r="F32" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="M32" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="P32" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="B33" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C33" s="19" t="s">
+        <v>322</v>
+      </c>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="M33" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="P33" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="B34" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C34" s="19" t="s">
+        <v>324</v>
+      </c>
+      <c r="F34" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="M34" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="P34" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="B35" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C35" s="19" t="s">
+        <v>691</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="M35" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="P35" s="2" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="B36" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C36" s="19" t="s">
+        <v>700</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="F36" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="M36" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="P36" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+      <c r="B37" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C37" s="19" t="s">
+        <v>699</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="F37" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="M37" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="P37" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B38" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C38" s="19" t="s">
+        <v>330</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="F38" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="M38" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B39" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C39" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F39" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="K39" s="15" t="s">
+        <v>335</v>
+      </c>
+      <c r="M39" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N39" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P39" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="B40" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C40" s="19" t="s">
+        <v>336</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="F40" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="M40" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="P40" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="B41" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C41" s="19" t="s">
+        <v>342</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="F41" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="M41" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="P41" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B42" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C42" s="19" t="s">
+        <v>346</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="F42" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="M42" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="P42" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+      <c r="B43" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C43" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="F43" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="M43" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="P43" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B44" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C44" s="19" t="s">
+        <v>352</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="F44" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="M44" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="P44" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B45" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C45" s="19" t="s">
+        <v>355</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="F45" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="M45" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="P45" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="B46" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C46" s="19" t="s">
+        <v>359</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="F46" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="M46" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="P46" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="B47" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C47" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="F47" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="M47" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="P47" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B48" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C48" s="19" t="s">
+        <v>364</v>
+      </c>
+      <c r="F48" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="M48" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="P48" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="49" spans="2:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B49" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C49" s="19" t="s">
+        <v>365</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F49" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="M49" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="P49" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="50" spans="2:16" ht="85.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B50" s="17" t="s">
+        <v>369</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F50" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="M50" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="N50" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="O50" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="P50" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="51" spans="2:16" ht="84.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B51" s="17" t="s">
+        <v>369</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="F51" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="M51" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N51" s="18" t="s">
+        <v>379</v>
+      </c>
+      <c r="O51" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="P51" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="52" spans="2:16" ht="72" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="17" t="s">
+        <v>369</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="F52" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="M52" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N52" s="18" t="s">
+        <v>383</v>
+      </c>
+      <c r="P52" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="53" spans="2:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="17" t="s">
+        <v>369</v>
+      </c>
+      <c r="C53" s="13" t="s">
+        <v>384</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="F53" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="M53" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="N53" s="15" t="s">
+        <v>387</v>
+      </c>
+      <c r="O53" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="P53" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="54" spans="2:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B54" s="17" t="s">
+        <v>369</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>388</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="F54" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="M54" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="P54" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="55" spans="2:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B55" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="C55" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="F55" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="M55" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N55" s="18" t="s">
+        <v>394</v>
+      </c>
+      <c r="P55" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="56" spans="2:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B56" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="C56" s="13" t="s">
+        <v>395</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="F56" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="M56" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="P56" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="57" spans="2:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B57" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="C57" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="F57" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="M57" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N57" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="P57" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="58" spans="2:16" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>401</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="F58" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="M58" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="P58" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="59" spans="2:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B59" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>404</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="F59" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="M59" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="P59" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="60" spans="2:16" ht="130.19999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="F60" s="14"/>
+      <c r="M60" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N60" s="18" t="s">
+        <v>408</v>
+      </c>
+      <c r="P60" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="61" spans="2:16" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B61" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="C61" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="F61" s="14"/>
+      <c r="M61" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N61" s="18" t="s">
+        <v>411</v>
+      </c>
+      <c r="P61" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="62" spans="2:16" ht="291.60000000000002" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B62" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="C62" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="F62" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="M62" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N62" s="18" t="s">
+        <v>417</v>
+      </c>
+      <c r="P62" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="63" spans="2:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="C63" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="F63" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="M63" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N63" s="18" t="s">
+        <v>419</v>
+      </c>
+      <c r="P63" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="2:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B64" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="C64" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="D64" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="F64" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="M64" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N64" s="18" t="s">
+        <v>422</v>
+      </c>
+      <c r="P64" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B65" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="C65" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="F65" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="M65" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N65" s="18" t="s">
+        <v>425</v>
+      </c>
+      <c r="P65" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" ht="144" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B66" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="C66" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="F66" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="M66" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N66" s="18" t="s">
+        <v>428</v>
+      </c>
+      <c r="P66" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" ht="187.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="C67" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="F67" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="M67" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N67" s="18" t="s">
+        <v>431</v>
+      </c>
+      <c r="P67" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" ht="129.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B68" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="C68" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="F68" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="M68" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N68" s="18" t="s">
+        <v>434</v>
+      </c>
+      <c r="P68" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" ht="72" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="C69" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="F69" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L69" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="M69" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N69" s="18" t="s">
+        <v>438</v>
+      </c>
+      <c r="P69" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" ht="72" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B70" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="C70" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="F70" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="M70" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N70" s="18" t="s">
+        <v>440</v>
+      </c>
+      <c r="P70" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="F71" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="M71" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N71" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="P71" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+    </row>
+    <row r="72" spans="1:16" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B72" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="C72" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="F72" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="M72" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N72" s="18" t="s">
+        <v>447</v>
+      </c>
+      <c r="P72" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B73" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="C73" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="F73" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="M73" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N73" s="18" t="s">
+        <v>449</v>
+      </c>
+      <c r="P73" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" ht="72" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B74" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="F74" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="M74" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N74" s="18" t="s">
+        <v>452</v>
+      </c>
+      <c r="P74" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="C75" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="F75" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="M75" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N75" s="18" t="s">
+        <v>455</v>
+      </c>
+      <c r="P75" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B76" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="C76" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="F76" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="M76" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N76" s="18" t="s">
+        <v>457</v>
+      </c>
+      <c r="P76" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" ht="74.400000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B77" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="C77" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="F77" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="M77" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N77" s="18" t="s">
+        <v>460</v>
+      </c>
+      <c r="P77" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" ht="172.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B78" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="C78" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="F78" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="M78" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N78" s="18" t="s">
+        <v>463</v>
+      </c>
+      <c r="P78" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="C79" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="F79" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="M79" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N79" s="18" t="s">
+        <v>466</v>
+      </c>
+      <c r="P79" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A80" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B80" s="23" t="s">
+        <v>468</v>
+      </c>
+      <c r="C80" s="13" t="s">
+        <v>469</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="F80" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="M80" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="P80" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A81" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B81" s="23" t="s">
+        <v>468</v>
+      </c>
+      <c r="C81" s="13" t="s">
+        <v>471</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="F81" s="22" t="s">
+        <v>399</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L81" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="M81" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="P81" s="2" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+      <c r="A82" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B82" s="23" t="s">
+        <v>468</v>
+      </c>
+      <c r="C82" s="13" t="s">
+        <v>475</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="F82" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L82" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="M82" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="P82" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A83" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B83" s="23" t="s">
+        <v>468</v>
+      </c>
+      <c r="C83" s="13" t="s">
+        <v>480</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="F83" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L83" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="M83" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="P83" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B84" s="23" t="s">
+        <v>468</v>
+      </c>
+      <c r="C84" s="13" t="s">
+        <v>484</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="F84" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="L84" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="M84" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="N84" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P84" s="2" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A85" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B85" s="23" t="s">
+        <v>468</v>
+      </c>
+      <c r="C85" s="13" t="s">
+        <v>489</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="F85" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L85" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="M85" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="P85" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A86" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B86" s="23" t="s">
+        <v>468</v>
+      </c>
+      <c r="C86" s="13" t="s">
+        <v>494</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="F86" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="M86" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="P86" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A87" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B87" s="23" t="s">
+        <v>468</v>
+      </c>
+      <c r="C87" s="13" t="s">
+        <v>496</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="F87" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L87" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="M87" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="P87" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B88" s="23" t="s">
+        <v>468</v>
+      </c>
+      <c r="C88" s="13" t="s">
+        <v>500</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="F88" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="M88" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="P88" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A89" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B89" s="23" t="s">
+        <v>468</v>
+      </c>
+      <c r="C89" s="13" t="s">
+        <v>502</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="F89" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="M89" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="P89" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+      <c r="A90" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B90" s="23" t="s">
+        <v>468</v>
+      </c>
+      <c r="C90" s="13" t="s">
+        <v>504</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="F90" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L90" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="M90" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="P90" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A91" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B91" s="23" t="s">
+        <v>468</v>
+      </c>
+      <c r="C91" s="13" t="s">
+        <v>508</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="F91" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="M91" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="P91" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B92" s="23" t="s">
+        <v>468</v>
+      </c>
+      <c r="C92" s="13" t="s">
+        <v>510</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="F92" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="L92" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="M92" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="P92" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B93" s="23" t="s">
+        <v>468</v>
+      </c>
+      <c r="C93" s="13" t="s">
+        <v>514</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="F93" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L93" s="5" t="s">
+        <v>517</v>
+      </c>
+      <c r="M93" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N93" s="2"/>
+      <c r="P93" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B94" s="23" t="s">
+        <v>468</v>
+      </c>
+      <c r="C94" s="13" t="s">
+        <v>518</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="F94" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="L94" s="2">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="M94" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N94" s="2"/>
+      <c r="P94" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A95" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B95" s="23" t="s">
+        <v>468</v>
+      </c>
+      <c r="C95" s="13" t="s">
+        <v>520</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="F95" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="J95" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="L95" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M95" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="P95" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A96" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B96" s="23" t="s">
+        <v>468</v>
+      </c>
+      <c r="C96" s="13" t="s">
+        <v>524</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="F96" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="M96" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="P96" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B97" s="23" t="s">
+        <v>468</v>
+      </c>
+      <c r="C97" s="13" t="s">
+        <v>526</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="F97" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="M97" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="P97" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A98" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B98" s="23" t="s">
+        <v>468</v>
+      </c>
+      <c r="C98" s="13" t="s">
+        <v>528</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="F98" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="M98" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="P98" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A99" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B99" s="23" t="s">
+        <v>468</v>
+      </c>
+      <c r="C99" s="13" t="s">
+        <v>530</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="F99" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="M99" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N99" s="2"/>
+      <c r="P99" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A100" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B100" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C100" s="13" t="s">
+        <v>533</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="J100" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="K100" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="M100" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N100" s="2"/>
+      <c r="P100" s="2" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" ht="54.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B101" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C101" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="F101" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="L101" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="M101" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N101" s="18" t="s">
+        <v>541</v>
+      </c>
+      <c r="P101" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" ht="72" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B102" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C102" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="F102" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="L102" s="20" t="s">
+        <v>545</v>
+      </c>
+      <c r="M102" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N102" s="18" t="s">
+        <v>546</v>
+      </c>
+      <c r="O102" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="P102" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B103" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C103" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="F103" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="L103" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="M103" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N103" s="18" t="s">
+        <v>550</v>
+      </c>
+      <c r="P103" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B104" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C104" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="F104" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="J104" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="M104" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N104" s="18" t="s">
+        <v>553</v>
+      </c>
+      <c r="P104" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B105" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C105" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="F105" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="J105" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="M105" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N105" s="18" t="s">
+        <v>557</v>
+      </c>
+      <c r="P105" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B106" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C106" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="F106" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="M106" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N106" s="18" t="s">
+        <v>559</v>
+      </c>
+      <c r="P106" s="2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B107" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C107" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="F107" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="J107" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="M107" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N107" s="18" t="s">
+        <v>562</v>
+      </c>
+      <c r="P107" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B108" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="F108" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="J108" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="M108" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N108" s="18" t="s">
+        <v>564</v>
+      </c>
+      <c r="P108" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B109" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C109" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="F109" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="M109" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N109" s="18" t="s">
+        <v>566</v>
+      </c>
+      <c r="P109" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B110" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C110" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="F110" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="H110" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="K110" s="20"/>
+      <c r="L110" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="M110" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N110" s="18" t="s">
+        <v>569</v>
+      </c>
+      <c r="O110" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="P110" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" ht="72" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B111" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C111" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="F111" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="M111" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N111" s="18" t="s">
+        <v>571</v>
+      </c>
+      <c r="P111" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B112" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C112" s="13" t="s">
+        <v>572</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="F112" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="M112" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N112" s="2"/>
+      <c r="P112" s="2" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A113" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B113" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C113" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="F113" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="M113" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N113" s="2"/>
+      <c r="P113" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B114" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C114" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="F114" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="H114" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="K114" s="20"/>
+      <c r="M114" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N114" s="18" t="s">
+        <v>579</v>
+      </c>
+      <c r="P114" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B115" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C115" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="F115" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="M115" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N115" s="18" t="s">
+        <v>582</v>
+      </c>
+      <c r="P115" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B116" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C116" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="F116" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="M116" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N116" s="18" t="s">
+        <v>585</v>
+      </c>
+      <c r="P116" s="6" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A117" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B117" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C117" s="13" t="s">
+        <v>586</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="F117" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L117" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="M117" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N117" s="2"/>
+      <c r="P117" s="2" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B118" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C118" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="F118" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="M118" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N118" s="18" t="s">
+        <v>292</v>
+      </c>
+      <c r="P118" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B119" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C119" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="F119" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="M119" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N119" s="18" t="s">
+        <v>593</v>
+      </c>
+      <c r="P119" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B120" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C120" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="F120" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="M120" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N120" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="P120" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B121" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C121" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="F121" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="M121" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N121" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="P121" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B122" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="C122" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="F122" s="14"/>
+      <c r="M122" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N122" s="18" t="s">
+        <v>598</v>
+      </c>
+      <c r="P122" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B123" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C123" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="F123" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="M123" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N123" s="18" t="s">
+        <v>601</v>
+      </c>
+      <c r="P123" s="2">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" ht="113.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B124" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C124" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="F124" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="M124" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N124" s="18" t="s">
+        <v>604</v>
+      </c>
+      <c r="P124" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A125" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B125" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C125" s="13" t="s">
+        <v>605</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="F125" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="M125" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N125" s="2"/>
+      <c r="P125" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="Q125" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A126" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B126" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C126" s="13" t="s">
+        <v>607</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="F126" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="M126" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N126" s="2"/>
+      <c r="P126" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A127" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B127" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C127" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="F127" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="M127" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N127" s="2"/>
+      <c r="P127" s="2">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A128" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B128" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C128" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="F128" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="M128" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N128" s="2"/>
+      <c r="P128" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B129" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C129" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="F129" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="M129" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N129" s="18" t="s">
+        <v>615</v>
+      </c>
+      <c r="P129" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B130" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C130" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="F130" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L130" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="M130" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N130" s="18" t="s">
+        <v>618</v>
+      </c>
+      <c r="P130" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A131" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B131" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C131" s="13" t="s">
+        <v>619</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="F131" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="L131" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="M131" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N131" s="2"/>
+      <c r="P131" s="2" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A132" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B132" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C132" s="13" t="s">
+        <v>622</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="F132" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="L132" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="M132" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N132" s="2"/>
+      <c r="P132" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A133" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B133" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C133" s="13" t="s">
+        <v>623</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="F133" s="22" t="s">
+        <v>399</v>
+      </c>
+      <c r="M133" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N133" s="2"/>
+      <c r="P133" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A134" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B134" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C134" s="13" t="s">
+        <v>625</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="F134" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="M134" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N134" s="2"/>
+      <c r="P134" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A135" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B135" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C135" s="13" t="s">
+        <v>627</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="F135" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="M135" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N135" s="2"/>
+      <c r="P135" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A136" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B136" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C136" s="13" t="s">
+        <v>629</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="F136" s="22" t="s">
+        <v>399</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="M136" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N136" s="2"/>
+      <c r="P136" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A137" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B137" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C137" s="13" t="s">
+        <v>631</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="F137" s="22" t="s">
+        <v>399</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="M137" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N137" s="2"/>
+      <c r="P137" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A138" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B138" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C138" s="13" t="s">
+        <v>633</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="F138" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="M138" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N138" s="2"/>
+      <c r="P138" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A139" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B139" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C139" s="13" t="s">
+        <v>636</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="F139" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="M139" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N139" s="2"/>
+      <c r="P139" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B140" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C140" s="13" t="s">
+        <v>638</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="F140" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="M140" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="N140" s="15" t="s">
+        <v>641</v>
+      </c>
+      <c r="P140" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A141" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B141" s="25" t="s">
+        <v>642</v>
+      </c>
+      <c r="C141" s="13" t="s">
+        <v>643</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="F141" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="M141" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N141" s="2"/>
+      <c r="P141" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A142" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B142" s="25" t="s">
+        <v>642</v>
+      </c>
+      <c r="C142" s="13" t="s">
+        <v>645</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="F142" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="M142" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N142" s="2"/>
+      <c r="P142" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A143" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B143" s="26" t="s">
+        <v>647</v>
+      </c>
+      <c r="C143" s="13" t="s">
+        <v>648</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="F143" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="L143" s="2">
+        <v>1056</v>
+      </c>
+      <c r="M143" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N143" s="2"/>
+      <c r="P143" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A144" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B144" s="26" t="s">
+        <v>647</v>
+      </c>
+      <c r="C144" s="13" t="s">
+        <v>650</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="F144" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="L144" s="2">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="M144" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N144" s="2"/>
+      <c r="P144" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I2" t="s">
-        <v>78</v>
-      </c>
-      <c r="J2" t="s">
-        <v>76</v>
-      </c>
-      <c r="K2" t="s">
-        <v>79</v>
-      </c>
-      <c r="L2" t="s">
-        <v>80</v>
-      </c>
-      <c r="M2" t="s">
-        <v>81</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>-5445</v>
-      </c>
-      <c r="Q2">
-        <v>8850</v>
-      </c>
-      <c r="R2" t="s">
-        <v>82</v>
-      </c>
-      <c r="S2" t="s">
-        <v>83</v>
-      </c>
-      <c r="T2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D3" t="s">
-        <v>86</v>
-      </c>
-      <c r="K3" t="s">
-        <v>87</v>
-      </c>
-      <c r="L3" t="s">
-        <v>88</v>
-      </c>
-      <c r="M3" t="s">
-        <v>89</v>
-      </c>
-      <c r="N3">
-        <v>60</v>
-      </c>
-      <c r="O3">
-        <v>100</v>
-      </c>
-      <c r="P3">
-        <v>41.107500000000002</v>
-      </c>
-      <c r="Q3">
-        <v>10.907166999999999</v>
-      </c>
-      <c r="R3" t="s">
-        <v>82</v>
+    </row>
+    <row r="145" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A145" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B145" s="26" t="s">
+        <v>647</v>
+      </c>
+      <c r="C145" s="13" t="s">
+        <v>652</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="F145" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L145" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="M145" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N145" s="2"/>
+      <c r="P145" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A146" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B146" s="26" t="s">
+        <v>647</v>
+      </c>
+      <c r="C146" s="13" t="s">
+        <v>655</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="F146" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="M146" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N146" s="2"/>
+      <c r="P146" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A147" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B147" s="26" t="s">
+        <v>647</v>
+      </c>
+      <c r="C147" s="13" t="s">
+        <v>657</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="F147" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="M147" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="N147" s="2"/>
+      <c r="P147" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A148" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="B148" s="11" t="s">
+        <v>659</v>
+      </c>
+      <c r="C148" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="F148" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="J148" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="M148" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N148" s="18" t="s">
+        <v>661</v>
+      </c>
+      <c r="P148" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A149" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="B149" s="11" t="s">
+        <v>659</v>
+      </c>
+      <c r="C149" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="M149" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N149" s="18" t="s">
+        <v>664</v>
+      </c>
+      <c r="P149" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="B150" s="11" t="s">
+        <v>659</v>
+      </c>
+      <c r="C150" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="M150" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N150" s="18" t="s">
+        <v>666</v>
+      </c>
+      <c r="P150" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="B151" s="11" t="s">
+        <v>659</v>
+      </c>
+      <c r="C151" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="M151" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="N151" s="18" t="s">
+        <v>667</v>
+      </c>
+      <c r="P151" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B152" s="17" t="s">
+        <v>668</v>
+      </c>
+      <c r="C152" s="13" t="s">
+        <v>669</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="F152" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H152" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="L152" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="M152" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="N152" s="2"/>
+      <c r="P152" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="B153" s="11" t="s">
+        <v>673</v>
+      </c>
+      <c r="C153" s="13" t="s">
+        <v>674</v>
+      </c>
+      <c r="F153" s="14"/>
+      <c r="M153" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="N153" s="2"/>
+      <c r="P153" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="154" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A154" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="B154" s="11" t="s">
+        <v>673</v>
+      </c>
+      <c r="C154" s="27" t="s">
+        <v>676</v>
+      </c>
+      <c r="M154" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="N154" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P154" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="155" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A155" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="B155" s="11" t="s">
+        <v>673</v>
+      </c>
+      <c r="C155" s="27" t="s">
+        <v>677</v>
+      </c>
+      <c r="M155" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="N155" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P155" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A156" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="B156" s="11" t="s">
+        <v>673</v>
+      </c>
+      <c r="C156" s="27" t="s">
+        <v>678</v>
+      </c>
+      <c r="H156" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="M156" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="N156" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P156" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="157" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A157" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="B157" s="11" t="s">
+        <v>673</v>
+      </c>
+      <c r="C157" s="27" t="s">
+        <v>679</v>
+      </c>
+      <c r="M157" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="N157" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P157" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A158" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="B158" s="11" t="s">
+        <v>673</v>
+      </c>
+      <c r="C158" s="27" t="s">
+        <v>680</v>
+      </c>
+      <c r="M158" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="N158" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P158" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A159" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="B159" s="11" t="s">
+        <v>673</v>
+      </c>
+      <c r="C159" s="27" t="s">
+        <v>681</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="H159" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="M159" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="N159" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P159" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A160" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="B160" s="11" t="s">
+        <v>673</v>
+      </c>
+      <c r="C160" s="27" t="s">
+        <v>683</v>
+      </c>
+      <c r="M160" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="N160" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P160" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="161" spans="1:16" s="34" customFormat="1" ht="72" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A161" s="28" t="s">
+        <v>254</v>
+      </c>
+      <c r="B161" s="29" t="s">
+        <v>684</v>
+      </c>
+      <c r="C161" s="30" t="s">
+        <v>685</v>
+      </c>
+      <c r="D161" s="31" t="s">
+        <v>686</v>
+      </c>
+      <c r="E161" s="31"/>
+      <c r="F161" s="32" t="s">
+        <v>186</v>
+      </c>
+      <c r="G161" s="31"/>
+      <c r="H161" s="31" t="s">
+        <v>179</v>
+      </c>
+      <c r="I161" s="28"/>
+      <c r="J161" s="31"/>
+      <c r="K161" s="31"/>
+      <c r="L161" s="31" t="s">
+        <v>687</v>
+      </c>
+      <c r="M161" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="N161" s="33" t="s">
+        <v>688</v>
+      </c>
+      <c r="O161" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="P161" s="31" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="162" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A162" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B162" s="11" t="s">
+        <v>726</v>
+      </c>
+      <c r="C162" s="27" t="s">
+        <v>707</v>
+      </c>
+      <c r="D162" s="35" t="s">
+        <v>721</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="F162" s="32" t="s">
+        <v>186</v>
+      </c>
+      <c r="H162" s="31" t="s">
+        <v>179</v>
+      </c>
+      <c r="J162" s="11"/>
+      <c r="K162" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="L162" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="M162" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="P162" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A163" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B163" s="11" t="s">
+        <v>726</v>
+      </c>
+      <c r="C163" s="27" t="s">
+        <v>712</v>
+      </c>
+      <c r="D163" s="35" t="s">
+        <v>723</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="F163" s="32" t="s">
+        <v>186</v>
+      </c>
+      <c r="H163" s="31" t="s">
+        <v>179</v>
+      </c>
+      <c r="J163" s="11"/>
+      <c r="K163" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="L163" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="M163" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="P163" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A164" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B164" s="11" t="s">
+        <v>726</v>
+      </c>
+      <c r="C164" s="27" t="s">
+        <v>713</v>
+      </c>
+      <c r="D164" s="35" t="s">
+        <v>722</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="F164" s="32" t="s">
+        <v>186</v>
+      </c>
+      <c r="H164" s="31" t="s">
+        <v>179</v>
+      </c>
+      <c r="J164" s="11"/>
+      <c r="K164" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="L164" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="M164" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="P164" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="165" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A165" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B165" s="11" t="s">
+        <v>726</v>
+      </c>
+      <c r="C165" s="27" t="s">
+        <v>714</v>
+      </c>
+      <c r="J165" s="11"/>
+      <c r="P165" s="2" t="s">
+        <v>725</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:Q165" xr:uid="{D65FE3B8-EA9F-4A1C-8B4E-F3566D1718E8}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="asmr:analyzedAreaUnit"/>
+        <filter val="asmr:analyzedAreaValue"/>
+        <filter val="asmr:analyzedTime"/>
+        <filter val="asmr:armLength"/>
+        <filter val="asmr:bait"/>
+        <filter val="asmr:baitQuantity"/>
+        <filter val="asmr:batterySystem"/>
+        <filter val="asmr:cameraSystem"/>
+        <filter val="asmr:canisterModel"/>
+        <filter val="asmr:costAnalysisCurrency"/>
+        <filter val="asmr:costAnalysisUnit"/>
+        <filter val="asmr:costPerCostAnalysisUnit"/>
+        <filter val="asmr:divingGasMix"/>
+        <filter val="asmr:ecologicalParameters"/>
+        <filter val="asmr:ecoregionCode"/>
+        <filter val="asmr:ecoregionName"/>
+        <filter val="asmr:ecoregionScheme"/>
+        <filter val="asmr:equipmentCostPerUnit"/>
+        <filter val="asmr:excludedSamplingEffortUnit"/>
+        <filter val="asmr:excludedSamplingEffortUnitRationale"/>
+        <filter val="asmr:excludedSubstrateScope"/>
+        <filter val="asmr:exSituAbioticParametersAnalyzed"/>
+        <filter val="asmr:fieldOfView"/>
+        <filter val="asmr:geomorphologicalContext"/>
+        <filter val="asmr:geomorphologyClassificationScheme"/>
+        <filter val="asmr:habitatClassificationScheme"/>
+        <filter val="asmr:inSituAbioticlParametersAnalyzed"/>
+        <filter val="asmr:inSituAbioticParametersCollected"/>
+        <filter val="asmr:lightSystem"/>
+        <filter val="asmr:manipulatorArms"/>
+        <filter val="asmr:maximumAnalyzedDepth"/>
+        <filter val="asmr:maximumSurveyedDepth"/>
+        <filter val="asmr:minimumAnalyzedDepth"/>
+        <filter val="asmr:minimumSurveyedDepth"/>
+        <filter val="asmr:navigationSpeed"/>
+        <filter val="asmr:otherFaunaAttraction"/>
+        <filter val="asmr:pelagicORbenthicBaitedPlatform"/>
+        <filter val="asmr:personnelCostPerUnit"/>
+        <filter val="asmr:physiographicContext"/>
+        <filter val="asmr:positioningSystem"/>
+        <filter val="asmr:protectedAreaOrOECM"/>
+        <filter val="asmr:protocolPreventionMeasures"/>
+        <filter val="asmr:protocolRisks"/>
+        <filter val="asmr:sampleContainer"/>
+        <filter val="asmr:samplingPlatform"/>
+        <filter val="asmr:samplingPlatformModel"/>
+        <filter val="asmr:sensors"/>
+        <filter val="asmr:sensorsCalibration"/>
+        <filter val="asmr:sizeReferenceSystem"/>
+        <filter val="asmr:spatialReplicates"/>
+        <filter val="asmr:standardFaciesValue"/>
+        <filter val="asmr:standardGeographicFeatureClassification"/>
+        <filter val="asmr:standardGeographicFeatureValue"/>
+        <filter val="asmr:standardHabitatValue"/>
+        <filter val="asmr:standardSubstrateClass"/>
+        <filter val="asmr:standardSubstrateGroup"/>
+        <filter val="asmr:standardSubstrateOrigin"/>
+        <filter val="asmr:standardSubstrateSubclass"/>
+        <filter val="asmr:standardTargetHabitatScope"/>
+        <filter val="asmr:substrateClassificationScheme"/>
+        <filter val="asmr:substrateScope"/>
+        <filter val="asmr:surveyedTime"/>
+        <filter val="asmr:surveyType"/>
+        <filter val="asmr:temporalReplicates"/>
+        <filter val="asmr:temporalScale"/>
+        <filter val="asmr:validationProtocolDescription"/>
+        <filter val="asmr:verbatimGeomorphologicalContext"/>
+        <filter val="asmr:verbatimHabitat"/>
+        <filter val="asmr:verbatimLithology"/>
+        <filter val="asmr:verbatimProtectionMeasures"/>
+        <filter val="asmr:verbatimSubstrate"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <hyperlinks>
+    <hyperlink ref="N10" r:id="rId1" xr:uid="{FE7BA7A2-708B-4BF5-AAC4-9AA8C158A135}"/>
+    <hyperlink ref="L16" r:id="rId2" xr:uid="{1D7C098B-C020-483C-9C6A-B8831B2E8513}"/>
+    <hyperlink ref="K39" r:id="rId3" xr:uid="{21124EAF-8D70-4DB6-A92C-5EE424CBFAAB}"/>
+    <hyperlink ref="N23" r:id="rId4" xr:uid="{2BC0160F-6F20-4C89-B362-60592BD7B1C1}"/>
+    <hyperlink ref="N24" r:id="rId5" xr:uid="{EFB0294F-CF01-4B2D-85C7-FF624A8E5D2E}"/>
+    <hyperlink ref="N25" r:id="rId6" xr:uid="{4653923B-8C55-4BB3-B857-52B8C3CBF8E1}"/>
+    <hyperlink ref="N26" r:id="rId7" xr:uid="{ACAEF176-8FDB-43B5-84E2-F9757C46DB07}"/>
+    <hyperlink ref="N27" r:id="rId8" xr:uid="{E4ABC6B3-8474-45FE-84E6-246681820053}"/>
+    <hyperlink ref="N51" r:id="rId9" xr:uid="{1D2FCFEA-2148-40AD-B572-F7CB8238A534}"/>
+    <hyperlink ref="N52" r:id="rId10" xr:uid="{8E57B5D0-F78B-464A-9D84-3B5E85016CE6}"/>
+    <hyperlink ref="N55" r:id="rId11" xr:uid="{413F8BBC-9AF0-436C-B9AF-C322B4335146}"/>
+    <hyperlink ref="N57" r:id="rId12" xr:uid="{FFAC4E47-FAEC-472E-9C3F-0A8AF5505D03}"/>
+    <hyperlink ref="N60" r:id="rId13" xr:uid="{561738C7-9D2C-47D9-A3DD-1C82B9ADD6BD}"/>
+    <hyperlink ref="N61" r:id="rId14" xr:uid="{401147E0-4A62-4A1F-BB52-BD2F60A6479B}"/>
+    <hyperlink ref="N62" r:id="rId15" xr:uid="{A42E95CE-2A39-4AFF-89B1-4636F6F28A1E}"/>
+    <hyperlink ref="N63" r:id="rId16" xr:uid="{694C55CD-314C-4B7F-B660-198A27E3B905}"/>
+    <hyperlink ref="N64" r:id="rId17" xr:uid="{CD0EBF7E-57CD-4759-9685-E3AB0F99A33B}"/>
+    <hyperlink ref="N65" r:id="rId18" xr:uid="{9A4A428B-B3EC-4912-AE08-159F5F98AA5D}"/>
+    <hyperlink ref="N66" r:id="rId19" xr:uid="{4E809024-C6EB-43EB-88FA-53B97C5DDE7A}"/>
+    <hyperlink ref="N67" r:id="rId20" xr:uid="{0B789BFA-391F-4541-9F12-C3375C46F9D8}"/>
+    <hyperlink ref="N68" r:id="rId21" xr:uid="{49696606-BD9B-44F0-A529-054C1AC5A0F4}"/>
+    <hyperlink ref="N69" r:id="rId22" xr:uid="{FD948D41-AE23-46B5-A480-8421D4789136}"/>
+    <hyperlink ref="N70" r:id="rId23" xr:uid="{954472F0-59C0-47AC-A0BC-219411CC7BF0}"/>
+    <hyperlink ref="N71" r:id="rId24" xr:uid="{42E4D2F7-7A34-4B0C-AFC5-FC45951D2490}"/>
+    <hyperlink ref="N72" r:id="rId25" xr:uid="{5EE3ECD7-F096-426A-BFF9-2D87ADADCB33}"/>
+    <hyperlink ref="N73" r:id="rId26" xr:uid="{306CD129-DE7D-449C-B733-83E01E8E75E8}"/>
+    <hyperlink ref="N74" r:id="rId27" xr:uid="{8419D2B6-89AF-462F-AA8D-BEE548C3ACE8}"/>
+    <hyperlink ref="N75" r:id="rId28" xr:uid="{F3B97316-24C6-46AC-9669-4EA102866876}"/>
+    <hyperlink ref="N76" r:id="rId29" xr:uid="{2BF6FAE4-6730-4601-9AED-D5375AC0D44A}"/>
+    <hyperlink ref="N77" r:id="rId30" xr:uid="{DD6C8638-E8B4-458E-B022-930051242DF2}"/>
+    <hyperlink ref="N78" r:id="rId31" xr:uid="{F82DBFAB-DF46-42A4-9360-2627112FCCE1}"/>
+    <hyperlink ref="N79" r:id="rId32" xr:uid="{88F7C310-B664-49D7-B67A-76B540A90C1A}"/>
+    <hyperlink ref="N101" r:id="rId33" xr:uid="{8E33BDEA-1D55-4F1E-A9A3-DE00D7E41E7D}"/>
+    <hyperlink ref="N102" r:id="rId34" xr:uid="{D986E0A4-B008-4A29-B98B-9251BAAE4E63}"/>
+    <hyperlink ref="N103" r:id="rId35" xr:uid="{D7595955-C320-489C-96CC-37DF02B6A5B1}"/>
+    <hyperlink ref="N114" r:id="rId36" xr:uid="{9B693486-7EE8-4984-9BCD-2845A421FAFB}"/>
+    <hyperlink ref="N115" r:id="rId37" xr:uid="{6429CB6D-70B2-48B0-94DD-55013826650C}"/>
+    <hyperlink ref="N116" r:id="rId38" xr:uid="{65B19377-6FCD-498A-B8AF-811770FB2C80}"/>
+    <hyperlink ref="N118" r:id="rId39" xr:uid="{8AAECF83-49BA-4542-8FE2-DE7BF68F2206}"/>
+    <hyperlink ref="N119" r:id="rId40" xr:uid="{C6958E6A-FBA2-4277-BF4C-3041E39FFA96}"/>
+    <hyperlink ref="N120" r:id="rId41" xr:uid="{102353C4-A2C0-4137-A067-19CFC53BC7ED}"/>
+    <hyperlink ref="N121" r:id="rId42" xr:uid="{13C52733-7BC1-4186-83AA-4A198F35A169}"/>
+    <hyperlink ref="N123" r:id="rId43" xr:uid="{63BFA53D-402D-402C-928D-3E1FD7BCEAC8}"/>
+    <hyperlink ref="N124" r:id="rId44" xr:uid="{7C5BC85B-DA2C-4452-A902-440FB222F6B3}"/>
+    <hyperlink ref="N129" r:id="rId45" xr:uid="{99CA1951-0EFC-43B5-9216-406FA2E485F0}"/>
+    <hyperlink ref="N130" r:id="rId46" xr:uid="{779DEC38-F313-4D44-8112-5FA11982CDAA}"/>
+    <hyperlink ref="N105" r:id="rId47" xr:uid="{BA80BEB9-1BEB-43AC-A183-CFF87597F166}"/>
+    <hyperlink ref="N106" r:id="rId48" xr:uid="{F6C626A1-DBAA-434A-B30F-D9595D64A889}"/>
+    <hyperlink ref="N107" r:id="rId49" xr:uid="{02C39F71-F867-41DF-8A0A-B2A8ECA9DA94}"/>
+    <hyperlink ref="N148" r:id="rId50" xr:uid="{32AD3D12-C32B-460E-9FEC-61061E973F7E}"/>
+    <hyperlink ref="N151" r:id="rId51" xr:uid="{F8EE702C-F4AE-4D65-91C2-A8C8C01C7D26}"/>
+    <hyperlink ref="N149" r:id="rId52" xr:uid="{D72C4A05-8575-4E84-B498-37518FD57167}"/>
+    <hyperlink ref="N150" r:id="rId53" xr:uid="{033E5A83-E19E-4AA7-98BB-D005A3E40034}"/>
+    <hyperlink ref="N6" r:id="rId54" xr:uid="{9B647779-EC90-47F8-8D4E-90B928218B92}"/>
+    <hyperlink ref="N5" r:id="rId55" xr:uid="{C248B40E-F8FC-4A5F-A735-C57A565EE58B}"/>
+    <hyperlink ref="N3" r:id="rId56" location="dwc_recordedByID" xr:uid="{553B5BF8-D197-4734-8EEA-6491AC84F944}"/>
+    <hyperlink ref="N2" r:id="rId57" location="dwc_recordedBy" xr:uid="{E2A98DA4-D9E8-48CD-BA47-62F1F7133AF2}"/>
+    <hyperlink ref="N7" r:id="rId58" xr:uid="{3172B057-C480-46C3-B412-8224BD7063D3}"/>
+    <hyperlink ref="N11" r:id="rId59" xr:uid="{5C4D3B0F-B68F-45B4-8D42-417E67F4ECD8}"/>
+    <hyperlink ref="N12" r:id="rId60" xr:uid="{FE33CA91-0832-4269-A9E5-C931DA01A5FA}"/>
+    <hyperlink ref="N13" r:id="rId61" xr:uid="{EA3D18F4-652F-4AEB-B34A-4FD5FBB08B28}"/>
+    <hyperlink ref="N14" r:id="rId62" xr:uid="{1FE4ADFF-5F0E-4248-8DBC-5DCCECD652A9}"/>
+    <hyperlink ref="N161" r:id="rId63" xr:uid="{A4C94F78-87F2-4A44-B947-B4A791704F47}"/>
+    <hyperlink ref="N17" r:id="rId64" xr:uid="{8341A7E7-5F0A-413B-82A8-2F028BA38758}"/>
+    <hyperlink ref="N18" r:id="rId65" xr:uid="{B5C1B64D-EB51-4879-9688-1B12D731980A}"/>
+    <hyperlink ref="N19" r:id="rId66" xr:uid="{B771A82D-5175-48C0-9A38-37145F95186B}"/>
+    <hyperlink ref="N20" r:id="rId67" xr:uid="{A8A464D9-AD7A-40D6-84E3-D7DE816E7E1D}"/>
+    <hyperlink ref="N21" r:id="rId68" xr:uid="{5D960029-D253-4F88-8EE5-494CA250994B}"/>
+    <hyperlink ref="N22" r:id="rId69" xr:uid="{5E1C639D-CBE4-4040-A596-6B5E382E3734}"/>
+    <hyperlink ref="N53" r:id="rId70" xr:uid="{5C98C934-330C-45FE-9331-F72295536D56}"/>
+    <hyperlink ref="N140" r:id="rId71" xr:uid="{4312A502-3B69-4388-92B6-7920B54334BB}"/>
+    <hyperlink ref="N108" r:id="rId72" xr:uid="{7CE2B926-8BC1-4968-8353-EC27E522029E}"/>
+    <hyperlink ref="N111" r:id="rId73" xr:uid="{B5A99BB7-B8A3-4E3E-8469-F4D7030BB082}"/>
+    <hyperlink ref="N109" r:id="rId74" xr:uid="{C0FA38A5-F1E8-474C-80B1-92AB43F50AD2}"/>
+    <hyperlink ref="N110" r:id="rId75" xr:uid="{23F437CB-8D97-4B29-9355-7B6A9A336ED6}"/>
+    <hyperlink ref="N122" r:id="rId76" xr:uid="{1D15B6CB-6099-4F22-998F-186AB3C30800}"/>
+    <hyperlink ref="P3" r:id="rId77" xr:uid="{0404E210-B635-4E25-ACFB-D6B373346938}"/>
+    <hyperlink ref="P4" r:id="rId78" xr:uid="{91BF0873-DE2B-43CB-9DE0-FBB42DEF4E57}"/>
+    <hyperlink ref="P14" r:id="rId79" display="https://doi.org/10.1371/journal.pone.0016357" xr:uid="{D3E80C1F-0934-4CAE-8C98-A21DBB8695C1}"/>
+    <hyperlink ref="P116" r:id="rId80" display="https://doi.org/10.1371/journal.pone.0016357" xr:uid="{34032AFA-139C-4374-B3E3-D87690D2CC56}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId81"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A5FB38B-1CE1-4858-9552-E885DEB608FA}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A929A264-79BF-4A80-8B48-FBF349CD37CB}">
+  <dimension ref="A1:AA2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="31.21875" customWidth="1"/>
+    <col min="2" max="2" width="40.6640625" customWidth="1"/>
+    <col min="3" max="3" width="32.33203125" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" customWidth="1"/>
+    <col min="13" max="13" width="24.109375" customWidth="1"/>
+    <col min="21" max="21" width="13.88671875" customWidth="1"/>
+    <col min="22" max="22" width="16.6640625" customWidth="1"/>
+    <col min="25" max="25" width="29.77734375" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="V1" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="W1" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="X1" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="Y1" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="Z1" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="AA1" s="13" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D2" t="s">
+        <v>77</v>
+      </c>
+      <c r="K2" t="s">
+        <v>78</v>
+      </c>
+      <c r="L2" t="s">
+        <v>79</v>
+      </c>
+      <c r="M2" t="s">
+        <v>80</v>
+      </c>
+      <c r="N2">
+        <v>60</v>
+      </c>
+      <c r="O2">
+        <v>100</v>
+      </c>
+      <c r="P2">
+        <v>41.107500000000002</v>
+      </c>
+      <c r="Q2">
+        <v>10.907166999999999</v>
+      </c>
+      <c r="R2" t="s">
+        <v>75</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="V2" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="W2" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="V2" r:id="rId1" xr:uid="{2C1A592E-F22C-45C3-9CE1-37CD746EE4BB}"/>
+    <hyperlink ref="W2" r:id="rId2" xr:uid="{5ECA2A48-EFCE-4EC8-BD58-F7E8AB394AD8}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1584,22 +8722,22 @@
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="F2" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="G2" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K2" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="L2" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1709,13 +8847,13 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -1763,45 +8901,6 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{992C281F-3BD8-42F9-9BA5-8BC2801E0AD2}">
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDFEFAD3-80F1-4FAE-AB6E-17D311EB3EFD}">
   <dimension ref="A1:BF2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1825,258 +8924,258 @@
   <sheetData>
     <row r="1" spans="1:57" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="AF1" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="AH1" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AI1" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AK1" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AL1" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AM1" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AN1" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AO1" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AP1" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AR1" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AS1" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AT1" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AU1" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AV1" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="AW1" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AM1" s="3" t="s">
+      <c r="AX1" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="AY1" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="AZ1" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="AP1" s="3" t="s">
+      <c r="BA1" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="AQ1" s="3" t="s">
+      <c r="BB1" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="AR1" s="3" t="s">
+      <c r="BC1" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="AS1" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AT1" s="3" t="s">
+      <c r="BD1" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="AU1" s="3" t="s">
+      <c r="BE1" s="7" t="s">
         <v>139</v>
-      </c>
-      <c r="AV1" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="AW1" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="AX1" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="AY1" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="AZ1" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="BA1" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="BB1" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="BC1" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="BD1" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="BE1" s="7" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:57" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B2" s="2">
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="E2" s="2">
         <v>1</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="N2" s="2" t="b">
         <v>1</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="Q2" s="2" t="b">
         <v>1</v>
       </c>
       <c r="R2" s="5" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="S2" s="2" t="b">
         <v>1</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="V2" s="2" t="b">
         <v>0</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="Y2" s="2" t="b">
         <v>0</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AB2" s="2" t="b">
         <v>0</v>
@@ -2085,16 +9184,16 @@
         <v>0</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="AH2" s="2" t="b">
         <v>0</v>
@@ -2106,7 +9205,7 @@
         <v>69</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="AL2" s="2" t="b">
         <v>1</v>
@@ -2115,58 +9214,58 @@
         <v>100</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="AR2" s="6" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="AS2" s="2">
         <v>1</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="AX2" s="2">
         <v>1400</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="BB2" s="2" t="b">
         <v>1</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="BD2" s="2" t="b">
         <v>1</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
